--- a/docs/xlsx/jobs-2026-09-04.xlsx
+++ b/docs/xlsx/jobs-2026-09-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="525">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1564 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Advancement Director</t>
+  </si>
+  <si>
+    <t>Coastal Rivers Conservation Trust</t>
+  </si>
+  <si>
+    <t>Damariscotta, ME</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$100,000 - $115,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-advancement-director-damariscotta-maine/5897088092</t>
+  </si>
+  <si>
+    <t>Analyst II</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Victorville, CA</t>
+  </si>
+  <si>
+    <t>$6,031 - $7,775 per month</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-analyst-ii-victorville-california/2688707077</t>
+  </si>
+  <si>
+    <t>Associate Director of Government Relations, Southeast Region</t>
+  </si>
+  <si>
+    <t>American Rivers</t>
+  </si>
+  <si>
+    <t>Anywhere, NC</t>
+  </si>
+  <si>
+    <t>$73,200 - $89,400 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-director-of-government-relations-southeast-region-anywhere-north-carolina/6734540721</t>
+  </si>
+  <si>
+    <t>Associate Individual Giving Officer (West Coast)</t>
+  </si>
+  <si>
+    <t>National Forest Foundation</t>
+  </si>
+  <si>
+    <t>Remote, CA</t>
+  </si>
+  <si>
+    <t>$75,000 - $86,250 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-individual-giving-officer-west-coast-remote-california/8203043557</t>
+  </si>
+  <si>
+    <t>Bilingual Community Educator</t>
+  </si>
+  <si>
+    <t>Cal-Wood Education Center</t>
+  </si>
+  <si>
+    <t>Jamestown, CO</t>
+  </si>
+  <si>
+    <t>$21 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bilingual-community-educator-jamestown-colorado/2825680600</t>
+  </si>
+  <si>
+    <t>Bosque Field Technician</t>
+  </si>
+  <si>
+    <t>Tryfacta</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$14.71 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bosque-field-technician-albuquerque-new-mexico/9180052517</t>
+  </si>
+  <si>
+    <t>Brand &amp; Creative Content Director</t>
+  </si>
+  <si>
+    <t>Boone and Crockett Club</t>
+  </si>
+  <si>
+    <t>Missoula, MT</t>
+  </si>
+  <si>
+    <t>For more information on salary &amp; benefits, please e-mail careers@boone-crockett.org.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-brand--creative-content-director-missoula-montana/1935101435</t>
+  </si>
+  <si>
+    <t>Cascadia Prescribed Burn Association Coordinator</t>
+  </si>
+  <si>
+    <t>Ecological Services LLC</t>
+  </si>
+  <si>
+    <t>LEAVENWORTH, WA</t>
+  </si>
+  <si>
+    <t>$55,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-cascadia-prescribed-burn-association-coordinator-leavenworth-washington/5798125900</t>
+  </si>
+  <si>
+    <t>Communications and Engagement Manager</t>
+  </si>
+  <si>
+    <t>Catamount Trail Association</t>
+  </si>
+  <si>
+    <t>Waitsfield, VT</t>
+  </si>
+  <si>
+    <t>$51,000 - $54,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-and-engagement-manager-waitsfield-vermont/2716555613</t>
+  </si>
+  <si>
+    <t>Communications Specialist</t>
+  </si>
+  <si>
+    <t>Northwoods Land Trust</t>
+  </si>
+  <si>
+    <t>Eagle River, WI</t>
+  </si>
+  <si>
+    <t>$25 - $27 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-specialist-eagle-river-wisconsin/2610577688</t>
+  </si>
+  <si>
+    <t>Community Engagement Manager</t>
+  </si>
+  <si>
+    <t>$57,783.96 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-engagement-manager-jamestown-colorado/7815006925</t>
+  </si>
+  <si>
+    <t>Conservation Policy Analyst</t>
+  </si>
+  <si>
+    <t>Xerces Society Inc</t>
+  </si>
+  <si>
+    <t>Portland, Other</t>
+  </si>
+  <si>
+    <t>$34.07 per hour</t>
+  </si>
+  <si>
+    <t>policy-and-law-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-policy-analyst-portland-oregon/6246100039</t>
+  </si>
+  <si>
+    <t>District Manager</t>
+  </si>
+  <si>
+    <t>Polk Soil And Water Conservation District</t>
+  </si>
+  <si>
+    <t>Dallas, OR</t>
+  </si>
+  <si>
+    <t>$85,000 - $115,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-manager-dallas-oregon/8398797145</t>
+  </si>
+  <si>
+    <t>Field Technician</t>
+  </si>
+  <si>
+    <t>$28 - $32 per hour</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-technician-leavenworth-washington/4959258760</t>
+  </si>
+  <si>
+    <t>Full-time Horticulture &amp; Grounds Support</t>
+  </si>
+  <si>
+    <t>Annmarie Garden</t>
+  </si>
+  <si>
+    <t>Solomons, MD</t>
+  </si>
+  <si>
+    <t>$18 - $23 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-full-time-horticulture--grounds-support-solomons-maryland/5455155774</t>
+  </si>
+  <si>
+    <t>Horticulturist</t>
+  </si>
+  <si>
+    <t>San Diego Natural History Museum</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$27.32 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-horticulturist-san-diego-california/1069086832</t>
+  </si>
+  <si>
+    <t>Licensing Specialist</t>
+  </si>
+  <si>
+    <t>Kent Conservation District</t>
+  </si>
+  <si>
+    <t>Dover, DE</t>
+  </si>
+  <si>
+    <t>$37,471.40 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-licensing-specialist-dover-delaware/8124612848</t>
+  </si>
+  <si>
+    <t>Manager IV (Texas Freshwater Fisheries Visitor Center Manager)</t>
+  </si>
+  <si>
+    <t>Texas Parks &amp; Wildlife Department</t>
+  </si>
+  <si>
+    <t>Athens, TX</t>
+  </si>
+  <si>
+    <t>$8,386.88 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-manager-iv-texas-freshwater-fisheries-visitor-center-manager-athens-texas/3289276958</t>
+  </si>
+  <si>
+    <t>Marine Science Instructor -- Shared Housing, Meals, and Ocean Fun included</t>
+  </si>
+  <si>
+    <t>Seacamp</t>
+  </si>
+  <si>
+    <t>Big Pine Key, FL</t>
+  </si>
+  <si>
+    <t>$1,100 - $1,400 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-science-instructor----shared-housing-meals-and-ocean-fun-included-big-pine-key-florida/7563190367</t>
+  </si>
+  <si>
+    <t>Mariposa County Resource Conservation District Community Engagement Assistant</t>
+  </si>
+  <si>
+    <t>Sierra Nevada AmeriCorps Partnership Program</t>
+  </si>
+  <si>
+    <t>Mariposa, CA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$2,773 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-mariposa-county-resource-conservation-district-community-engagement-assistant-mariposa-california/5314342388</t>
+  </si>
+  <si>
+    <t>NR Forestry Specialist Senior - Silviculture</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>Blackduck, MN</t>
+  </si>
+  <si>
+    <t>$29.76 - $43.69 / hourly; $62,138 - $91,224 / annually</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nr-forestry-specialist-senior---silviculture-blackduck-minnesota/1649882933</t>
+  </si>
+  <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>Great Mountain Forest</t>
+  </si>
+  <si>
+    <t>Norfolk, CT</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-office-manager-norfolk-connecticut/3679012372</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Hobe Sound Nature Center</t>
+  </si>
+  <si>
+    <t>Hobe Sound, FL</t>
+  </si>
+  <si>
+    <t>$55,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-manager-hobe-sound-florida/7690452248</t>
+  </si>
+  <si>
+    <t>Outward Bound Adventures Outdoor &amp; Environmental Education and Youth Leadership Program Coordinator</t>
+  </si>
+  <si>
+    <t>Pasadena, CA</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outward-bound-adventures-outdoor--environmental-education-and-youth-leadership-program-coordinator-pasadena-california/6783137898</t>
+  </si>
+  <si>
+    <t>PacFIN Data Management Specialist</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$26.14 - $41.57 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-pacfin-data-management-specialist-portland-oregon/8764069638</t>
+  </si>
+  <si>
+    <t>Program Supervisor V (ShareLunker Program Coordinator/Outreach Supervisor)</t>
+  </si>
+  <si>
+    <t>$7,694.42 per month</t>
+  </si>
+  <si>
+    <t>fisheries-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-supervisor-v-sharelunker-program-coordinatoroutreach-supervisor-athens-texas/8331285553</t>
+  </si>
+  <si>
+    <t>Restoration and Recreation Technician</t>
+  </si>
+  <si>
+    <t>The Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Reno, NV</t>
+  </si>
+  <si>
+    <t>$2,707.68 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-and-recreation-technician-las-vegas-nevada/9734989445</t>
+  </si>
+  <si>
+    <t>Senior Communications Manager</t>
+  </si>
+  <si>
+    <t>American Littoral Society</t>
+  </si>
+  <si>
+    <t>Highlands, NJ</t>
+  </si>
+  <si>
+    <t>$68,000 - $78,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-communications-manager-highlands-new-jersey/6420004183</t>
+  </si>
+  <si>
+    <t>Sequoia Riverlands Trust Education Technician and Nursery Technician</t>
+  </si>
+  <si>
+    <t>Visalia, CA</t>
+  </si>
+  <si>
+    <t>botany-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sequoia-riverlands-trust-education-technician-and-nursery-technician-visalia-california/2522432891</t>
+  </si>
+  <si>
+    <t>Shasta Land Trust (SLT)- Land Conservation Program Assistant</t>
+  </si>
+  <si>
+    <t>Redding, CA</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-shasta-land-trust-slt--land-conservation-program-assistant-redding-california/2861437681</t>
+  </si>
+  <si>
+    <t>Water Resource Control Engineer</t>
+  </si>
+  <si>
+    <t>Richmond, CA</t>
+  </si>
+  <si>
+    <t>$6,488 - $12,152 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resource-control-engineer-richmond-california/3014641950</t>
+  </si>
+  <si>
+    <t>Watershed Program Coordinator</t>
+  </si>
+  <si>
+    <t>Park Conservation District</t>
+  </si>
+  <si>
+    <t>Livingston, MT</t>
+  </si>
+  <si>
+    <t>$22 - $28 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-program-coordinator-livingston-montana/8280921445</t>
+  </si>
+  <si>
+    <t>Watershed Stewardship Coordinator Western Shasta Resource Conservation District</t>
+  </si>
+  <si>
+    <t>Anderson, CA</t>
+  </si>
+  <si>
+    <t>botany-ecology-forestry-hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-stewardship-coordinator-western-shasta-resource-conservation-district-anderson-california/2649522669</t>
+  </si>
+  <si>
+    <t>Wildlife Biologist - Nuisance Wildlife</t>
+  </si>
+  <si>
+    <t>Wildernex LLC Wildlife Control</t>
+  </si>
+  <si>
+    <t>Dallas, TX</t>
+  </si>
+  <si>
+    <t>$45,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist---nuisance-wildlife-dallas-texas/4493536949</t>
+  </si>
+  <si>
+    <t>Year-Round Crew Member: Tennessee</t>
+  </si>
+  <si>
+    <t>Southern Appalachian Wilderness Stewards</t>
+  </si>
+  <si>
+    <t>Johnson City, TN</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-year-round-crew-member-tennessee-johnson-city-tennessee/3800913685</t>
+  </si>
+  <si>
+    <t>Youth Programs Coordinator</t>
+  </si>
+  <si>
+    <t>Dependent on experience and level of employment.</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-youth-programs-coordinator-waitsfield-vermont/8065866759</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General: Affirmative Litigation (3910)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Utica, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 87594.00 - 186493.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/e0b2b9f4c1574b469f03019817879584-assistant-attorney-general-affirmative-litigation-3910-new-york-state-office-of-the-attorney-general-utica</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General: Civil Litigation for NYS (3909)</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 90356.00 - 190493.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/8276ba9724374e97aee1293751dc5941-assistant-attorney-general-civil-litigation-for-nys-3909-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Director for Economic and Business Diplomacy, Center for New Middle East (CNME) Washington, DC</t>
+  </si>
+  <si>
+    <t>AJC</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Community Development, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66f4649363334c069c44c9b7a45ee882-assistant-director-for-economic-and-business-diplomacy-center-for-new-middle-east-cnme-washington-dc-ajc-washington</t>
+  </si>
+  <si>
+    <t>Associate</t>
+  </si>
+  <si>
+    <t>Isaacson, Miller</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Arts Music, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/766e81159a194d45a426accc077d886a-associate-isaacson-miller-san-francisco</t>
+  </si>
+  <si>
+    <t>Associate Director of Development</t>
+  </si>
+  <si>
+    <t>Essie Justice Group</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ddfdc1663d824d41a859e6499fca9264-associate-director-of-development-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3894c897b1a4c87959e9c4aa55f9eb0-associate-director-of-development-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>Associate Director of Organizing</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ccbe272081f42f2b1b020ed159583fd-associate-director-of-organizing-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0045c7a886004dcfb33acc4f25aef890-associate-director-of-organizing-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>ASSOCIATE SUPERVISING ATTORNEY, REMOVAL DEFENSE PROJECT</t>
+  </si>
+  <si>
+    <t>Catholic Migration Services</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 97880.62 - 117664.36/year</t>
+  </si>
+  <si>
+    <t>Community Development, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b762671e0c9d4582abc06fa907f16246-associate-supervising-attorney-removal-defense-project-catholic-migration-services-kings-county</t>
+  </si>
+  <si>
+    <t>Associate, Culture &amp; Sports</t>
+  </si>
+  <si>
+    <t>Meridian International Center</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a1e8ac1e2c894e47acfd44871f74a2fe-associate-culture-sports-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>Bilingual Paralegal - Social Security Income (SSI)</t>
+  </si>
+  <si>
+    <t>Legal Services of New Jersey</t>
+  </si>
+  <si>
+    <t>Edison, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 54000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b32c14c6f5154cb5a3bce7900e006e59-bilingual-paralegal-social-security-income-ssi-legal-services-of-new-jersey-edison</t>
+  </si>
+  <si>
+    <t>Certified Nursing Assistant</t>
+  </si>
+  <si>
+    <t>District of Columbia Department of Youth Rehabilitation Services</t>
+  </si>
+  <si>
+    <t>USD 46437.00 - 60999.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/b2c693a5f0564dfe9f6c7ef3e310e8f1-certified-nursing-assistant-district-of-columbia-department-of-youth-rehabilitation-services-washington</t>
+  </si>
+  <si>
+    <t>Chief Financial and Operations Officer</t>
+  </si>
+  <si>
+    <t>Landesa</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06d25b4d01814c4ea6414c3be4fdaa97-chief-financial-and-operations-officer-landesa-seattle</t>
+  </si>
+  <si>
+    <t>Client Navigator</t>
+  </si>
+  <si>
+    <t>EngageWell IPA</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6794b444f98948e0ae09437e2aacab04-client-navigator-engagewell-ipa-new-york</t>
+  </si>
+  <si>
+    <t>Client Services Coordinator</t>
+  </si>
+  <si>
+    <t>Shine Foundation Inc</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Crime Safety, Disaster Relief</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f17298a124e4964b60709192a253550-client-services-coordinator-shine-foundation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e75e75e1b83a40c8b8b199d55f2e2e46-communications-manager-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/788ee857f06c4b8c8f9fb11ad47a9ae1-communications-manager-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>Communications Manager, America Saves</t>
+  </si>
+  <si>
+    <t>Consumer Federation of America</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1be599308e9345678624475c03236b96-communications-manager-america-saves-consumer-federation-of-america-washington</t>
+  </si>
+  <si>
+    <t>Global Arts Live</t>
+  </si>
+  <si>
+    <t>Cambridge, MA</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1bcfd3ec02cc4be7bf1c472b3da43f72-community-engagement-manager-global-arts-live-cambridge</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f84b075f8c1943ce987f464584bb7d1a-community-organizer-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/741ff1ac64884c9a93c6253d82b4c138-community-organizer-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>Controller - Southern Maryland (hybrid flexibility)</t>
+  </si>
+  <si>
+    <t>Cornerstone Montgomery Inc.</t>
+  </si>
+  <si>
+    <t>Prince Frederick, Maryland</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Substance Abuse Addiction, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa722baf39684dd5af7beff42a7a25b4-controller-southern-maryland-hybrid-flexibility-cornerstone-montgomery-inc-prince-frederick</t>
+  </si>
+  <si>
+    <t>Coordinator, Academic Advising</t>
+  </si>
+  <si>
+    <t>Marist University</t>
+  </si>
+  <si>
+    <t>Poughkeepsie, New York</t>
+  </si>
+  <si>
+    <t>USD 62353.20 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0b60d36d1bb145f3a46a035d30526c39-coordinator-academic-advising-marist-university-poughkeepsie</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Common Ground Farm</t>
+  </si>
+  <si>
+    <t>Beacon, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/355761c58dc74c598817dea8d8b5e074-development-coordinator-common-ground-farm-beacon</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>American Alpine Club</t>
+  </si>
+  <si>
+    <t>USD 104000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29de850887fb4bb49467e8644aef4c40-development-director-american-alpine-club-golden</t>
+  </si>
+  <si>
+    <t>Radnor Memorial Library</t>
+  </si>
+  <si>
+    <t>Wayne, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/710a0f2d92e5445d9f76e44287b18086-development-director-radnor-memorial-library-wayne</t>
+  </si>
+  <si>
+    <t>Development Director-Los Angeles</t>
+  </si>
+  <si>
+    <t>LIFT</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9e92eef18fb40e8af63a08c0d2ab190-development-director-los-angeles-lift-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Pike Place Market Foundation</t>
+  </si>
+  <si>
+    <t>USD 100751.04 - 144196.20/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e225033477b4430b18dfd4864cdde73-director-of-development-pike-place-market-foundation-seattle</t>
+  </si>
+  <si>
+    <t>Director of Facilities</t>
+  </si>
+  <si>
+    <t>Ironwood Pig Sanctuary</t>
+  </si>
+  <si>
+    <t>Marana, Arizona</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bebc910a5bf84125bcab5820524a7c41-director-of-facilities-ironwood-pig-sanctuary-marana</t>
+  </si>
+  <si>
+    <t>Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>Wolf Performing Arts Center</t>
+  </si>
+  <si>
+    <t>Bryn Mawr, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3228a8f2fcf34f8d83b492c908554966-director-of-finance-and-operations-wolf-performing-arts-center-bryn-mawr</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>Grassroots Global Justice</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 63800.00 - 76975.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7df0173e750a44e2bb41363243791501-executive-assistant-grassroots-global-justice-washington</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Bike Walk Alliance of New Hampshire</t>
+  </si>
+  <si>
+    <t>Remote (New Hampshire)</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ecdae4920a1f46eea781e99282ea8dc6-executive-director-bike-walk-alliance-of-new-hampshire-concord</t>
+  </si>
+  <si>
+    <t>Shasta County Fire Safe Council</t>
+  </si>
+  <si>
+    <t>Redding, California</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Rural Areas, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a783d5d9129427998e6d0e94ba8214d-executive-director-shasta-county-fire-safe-council-redding</t>
+  </si>
+  <si>
+    <t>Pacific Hospital Preservation &amp; Development Authority (PHPDA)</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 210000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/11c2a2dad3df4bf2b2f760958bde1c6f-executive-director-pacific-hospital-preservation-development-authority-phpda-seattle</t>
+  </si>
+  <si>
+    <t>Finance and Operations Administrator</t>
+  </si>
+  <si>
+    <t>Asian Cultural Council</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12297560260a46bd9d9e82ab7a880c30-finance-and-operations-administrator-asian-cultural-council-new-york</t>
+  </si>
+  <si>
+    <t>Food Pantry Coordinator</t>
+  </si>
+  <si>
+    <t>Natick Service Council</t>
+  </si>
+  <si>
+    <t>Natick, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2afec880a6574bb3af65c012dcee023c-food-pantry-coordinator-natick-service-council-natick</t>
+  </si>
+  <si>
+    <t>Fundraising Database Associate</t>
+  </si>
+  <si>
+    <t>Everytown For Gun Safety</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d271b9695a9a4bd1b517d7b8eb95290e-fundraising-database-associate-everytown-for-gun-safety-new-york</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>North Country Food Co-op</t>
+  </si>
+  <si>
+    <t>Plattsburgh, New York</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/e33d9f82bf6e4baebf8e88f61eeecc7d-general-manager-north-country-food-co-op-plattsburgh</t>
+  </si>
+  <si>
+    <t>Government Relations Director</t>
+  </si>
+  <si>
+    <t>NETWORK Lobby for Catholic Social Justice</t>
+  </si>
+  <si>
+    <t>USD 103000.00 - 129000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Policy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e2783ae27e51455a8920ac49f2d9b2ad-government-relations-director-network-lobby-for-catholic-social-justice-washington</t>
+  </si>
+  <si>
+    <t>GreenWorks Director</t>
+  </si>
+  <si>
+    <t>Joe's Movement Emporium/World Arts Focus</t>
+  </si>
+  <si>
+    <t>Mount Rainier, Maryland</t>
+  </si>
+  <si>
+    <t>Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f860508eab64557aa086d22b55926d6-greenworks-director-joes-movement-emporiumworld-arts-focus-mount-rainier</t>
+  </si>
+  <si>
+    <t>Head of Grantmaking Operations</t>
+  </si>
+  <si>
+    <t>Centre for Effective Altruism</t>
+  </si>
+  <si>
+    <t>USD 157435.00 - 157435.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e797ce692dd149eca4049fc2f8801d74-head-of-grantmaking-operations-centre-for-effective-altruism-oxford</t>
+  </si>
+  <si>
+    <t>Healing to Advocacy Program Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66ebca4c0e3a46eeb4f64611c47354b7-healing-to-advocacy-program-manager-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a5fd3b59ab74457a79f76b7a3297e93-healing-to-advocacy-program-manager-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>Healthcare Associate</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/46179bb4c5f94f92b305c315a47ab404-healthcare-associate-isaacson-miller-boston</t>
+  </si>
+  <si>
+    <t>Houseman-Steward, Events</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8fa2503a86d9449dbec84c677968be85-houseman-steward-events-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>HR &amp; Office Administration Coordinator</t>
+  </si>
+  <si>
+    <t>Opus Dance Theatre and Community Services Inc.</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2dbac2a8aa754ee6829380d26372981e-hr-office-administration-coordinator-opus-dance-theatre-and-community-services-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Human Resources Director</t>
+  </si>
+  <si>
+    <t>Mennonite Central Committee</t>
+  </si>
+  <si>
+    <t>Akron, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b2d2c6ade579466785a248517230b7f9-human-resources-director-mennonite-central-committee-akron</t>
+  </si>
+  <si>
+    <t>Instructor or Assistant Professor - Library</t>
+  </si>
+  <si>
+    <t>LaGuardia Community College</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 54454.00 - 79298.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/58aa6a6151c1487f90175894a2afec81-instructor-or-assistant-professor-library-laguardia-community-college-queens-county</t>
+  </si>
+  <si>
+    <t>Non-Teaching Adjunct, Level 1 - Office of Institutional Advancement and Communications</t>
+  </si>
+  <si>
+    <t>The Graduate Center, CUNY</t>
+  </si>
+  <si>
+    <t>USD 60.78 - 60.78/hour</t>
+  </si>
+  <si>
+    <t>Communications Access, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0310d6b3e00641bc98988818e163b58c-non-teaching-adjunct-level-1-office-of-institutional-advancement-and-communications-the-graduate-center-cuny-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time Leadership Workshop Co-Facilitator</t>
+  </si>
+  <si>
+    <t>OneWorld Now!</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cfb6790a9d1e46cdb6e919d21526fd80-part-time-leadership-workshop-co-facilitator-oneworld-now-seattle</t>
+  </si>
+  <si>
+    <t>Part-Time Licensed Mental Health Counselor</t>
+  </si>
+  <si>
+    <t>Arab American Association of New York</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d5764eacec546319fa6e0f01fd5c863-part-time-licensed-mental-health-counselor-arab-american-association-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Part-Time Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 55.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/668edc5c7db4447e9cf9bc7f72e9e65a-part-time-staff-attorney-arab-american-association-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Program Manager, Dallas</t>
+  </si>
+  <si>
+    <t>Laureus Sport for Good Foundation USA</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/acbdad5eb16d4eff9fa6cb94717f3fe1-program-manager-dallas-laureus-sport-for-good-foundation-usa-dallas</t>
+  </si>
+  <si>
+    <t>Program Officer, Sports</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/04c2be85a5ee420b962250228c6766bb-program-officer-sports-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>Recruiting Specialist</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 56291.00 - 73106.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31fddc1b00a142d8a820eba8e348784b-recruiting-specialist-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>RED KETTLE PARTNERS DIRECTOR</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df486db988f94838a8c9596a15d0d430-red-kettle-partners-director-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Restorative Practices Specialist</t>
+  </si>
+  <si>
+    <t>Deep Center</t>
+  </si>
+  <si>
+    <t>Savannah, Georgia</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0654e041bba44b3bb9406799bf251ea-restorative-practices-specialist-deep-center-savannah</t>
+  </si>
+  <si>
+    <t>Senior Community Organizer</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff0958089291447ab71aa89bbe322efa-senior-community-organizer-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ed8299424b0462ebe8676b6706f6a47-senior-community-organizer-essie-justice-group-oakland</t>
+  </si>
+  <si>
+    <t>Senior Coordinator, Finance and Facilities (Hybrid)</t>
+  </si>
+  <si>
+    <t>National PACE Association</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b252314713d49ff9d26457ea01de290-senior-coordinator-finance-and-facilities-hybrid-national-pace-association-alexandria</t>
+  </si>
+  <si>
+    <t>Senior Coordinator, Office of Science and Research</t>
+  </si>
+  <si>
+    <t>NAMI (National Alliance on Mental Illness)</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/853617601249418090f1f064662c0f95-senior-coordinator-office-of-science-and-research-nami-national-alliance-on-mental-illness-arlington</t>
+  </si>
+  <si>
+    <t>SENIOR DIRECTOR OF CORPORATE AND FOUNDATION RELATIONS</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1afb530b2fa6446fb61c5a995c6a1757-senior-director-of-corporate-and-foundation-relations-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Senior Director of Strategic Communications, Brand and Marketing</t>
+  </si>
+  <si>
+    <t>Grameen America Inc</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Microfinance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2326bdffc6d4c11848432b4462b2142-senior-director-of-strategic-communications-brand-and-marketing-grameen-america-inc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Product &amp; Project Manager - FieldKit</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>USD 74880.00 - 74880.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3622274e62be4b9199d3cc9a0936423b-senior-product-project-manager-fieldkit-multiplier-los-angeles</t>
+  </si>
+  <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 18.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42ed78c97f9c4d5394bf8a0330f3aced-service-enriched-housing-super-hero-community-housing-resource-partners-inc-austin</t>
+  </si>
+  <si>
+    <t>Social Services Case worker</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54654c94c4ab4f9291dca8666506bb52-social-services-case-worker-arab-american-association-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Senior Staff Attorney, or Senior Counsel, Immigrants' Rights Project</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 96069.00 - 219104.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a76198df2d4146b0aecbb6bd5431b09c-staff-attorney-senior-staff-attorney-or-senior-counsel-immigrants-rights-project-american-civil-liberties-union-san-francisco</t>
+  </si>
+  <si>
+    <t>Strategic Initiatives Project Coordinator</t>
+  </si>
+  <si>
+    <t>Kenyon College</t>
+  </si>
+  <si>
+    <t>Gambier, Ohio</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05d17993529f4adc91ec6ad6817cfff8-strategic-initiatives-project-coordinator-kenyon-college-gambier</t>
+  </si>
+  <si>
+    <t>Supervising Financial Counselor</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 73718.00 - 79857.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54887050dbf947faa68e34e3353ee720-supervising-financial-counselor-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Training Institute Manager</t>
+  </si>
+  <si>
+    <t>Custom Collaborative</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/593aace4d15443a4b303eb1ca29092ca-training-institute-manager-custom-collaborative-new-york</t>
+  </si>
+  <si>
+    <t>Training Manager, Shoah Foundation Countering Antisemitism Lab</t>
+  </si>
+  <si>
+    <t>University of Southern California - Shoah Foundation</t>
+  </si>
+  <si>
+    <t>USD 109264.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b7bc2c44ebe41e7af51a44059fc6a08-training-manager-shoah-foundation-countering-antisemitism-lab-university-of-southern-california-shoah-foundation-washington</t>
+  </si>
+  <si>
+    <t>Vice President of Communications</t>
+  </si>
+  <si>
+    <t>Pure Earth/Blacksmith Institute</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d7d90053f3049b684998c572cf6db75-vice-president-of-communications-pure-earthblacksmith-institute-new-york</t>
+  </si>
+  <si>
+    <t>Washington Director of External Engagement</t>
+  </si>
+  <si>
+    <t>Israel Policy Forum</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b718ab5c58f47438fcad857f47ac30c-washington-director-of-external-engagement-israel-policy-forum-washington</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1605,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1631,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +1974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2013,874 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" t="s">
+        <v>178</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" t="s">
+        <v>182</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>187</v>
+      </c>
+      <c r="F35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" t="s">
+        <v>193</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +2936,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +2975,1762 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" t="s">
+        <v>215</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F11" t="s">
+        <v>209</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" t="s">
+        <v>247</v>
+      </c>
+      <c r="F12" t="s">
+        <v>204</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" t="s">
+        <v>251</v>
+      </c>
+      <c r="F13" t="s">
+        <v>252</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D15" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" t="s">
+        <v>264</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" t="s">
+        <v>268</v>
+      </c>
+      <c r="F16" t="s">
+        <v>269</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" t="s">
+        <v>272</v>
+      </c>
+      <c r="F17" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" t="s">
+        <v>272</v>
+      </c>
+      <c r="F18" t="s">
+        <v>227</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>275</v>
+      </c>
+      <c r="B19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" t="s">
+        <v>277</v>
+      </c>
+      <c r="F19" t="s">
+        <v>278</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>280</v>
+      </c>
+      <c r="C20" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" t="s">
+        <v>282</v>
+      </c>
+      <c r="F20" t="s">
+        <v>283</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" t="s">
+        <v>225</v>
+      </c>
+      <c r="D21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" t="s">
+        <v>286</v>
+      </c>
+      <c r="F21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C22" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" t="s">
+        <v>286</v>
+      </c>
+      <c r="F22" t="s">
+        <v>227</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>289</v>
+      </c>
+      <c r="B23" t="s">
+        <v>290</v>
+      </c>
+      <c r="C23" t="s">
+        <v>291</v>
+      </c>
+      <c r="D23" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" t="s">
+        <v>292</v>
+      </c>
+      <c r="F23" t="s">
+        <v>293</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B24" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" t="s">
+        <v>297</v>
+      </c>
+      <c r="D24" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" t="s">
+        <v>298</v>
+      </c>
+      <c r="F24" t="s">
+        <v>299</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>301</v>
+      </c>
+      <c r="B25" t="s">
+        <v>302</v>
+      </c>
+      <c r="C25" t="s">
+        <v>303</v>
+      </c>
+      <c r="D25" t="s">
+        <v>304</v>
+      </c>
+      <c r="E25" t="s">
+        <v>305</v>
+      </c>
+      <c r="F25" t="s">
+        <v>306</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>308</v>
+      </c>
+      <c r="B26" t="s">
+        <v>309</v>
+      </c>
+      <c r="C26" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" t="s">
+        <v>310</v>
+      </c>
+      <c r="F26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>308</v>
+      </c>
+      <c r="B27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" t="s">
+        <v>314</v>
+      </c>
+      <c r="D27" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" t="s">
+        <v>282</v>
+      </c>
+      <c r="F27" t="s">
+        <v>315</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>317</v>
+      </c>
+      <c r="B28" t="s">
+        <v>318</v>
+      </c>
+      <c r="C28" t="s">
+        <v>225</v>
+      </c>
+      <c r="D28" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" t="s">
+        <v>319</v>
+      </c>
+      <c r="F28" t="s">
+        <v>320</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B29" t="s">
+        <v>323</v>
+      </c>
+      <c r="C29" t="s">
+        <v>256</v>
+      </c>
+      <c r="D29" t="s">
+        <v>202</v>
+      </c>
+      <c r="E29" t="s">
+        <v>324</v>
+      </c>
+      <c r="F29" t="s">
+        <v>325</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>327</v>
+      </c>
+      <c r="B30" t="s">
+        <v>328</v>
+      </c>
+      <c r="C30" t="s">
+        <v>329</v>
+      </c>
+      <c r="D30" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" t="s">
+        <v>330</v>
+      </c>
+      <c r="F30" t="s">
+        <v>331</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>333</v>
+      </c>
+      <c r="B31" t="s">
+        <v>334</v>
+      </c>
+      <c r="C31" t="s">
+        <v>335</v>
+      </c>
+      <c r="D31" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" t="s">
+        <v>336</v>
+      </c>
+      <c r="F31" t="s">
+        <v>337</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>339</v>
+      </c>
+      <c r="B32" t="s">
+        <v>340</v>
+      </c>
+      <c r="C32" t="s">
+        <v>341</v>
+      </c>
+      <c r="D32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32" t="s">
+        <v>342</v>
+      </c>
+      <c r="F32" t="s">
+        <v>209</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>344</v>
+      </c>
+      <c r="B33" t="s">
+        <v>345</v>
+      </c>
+      <c r="C33" t="s">
+        <v>346</v>
+      </c>
+      <c r="D33" t="s">
+        <v>304</v>
+      </c>
+      <c r="E33" t="s">
+        <v>347</v>
+      </c>
+      <c r="F33" t="s">
+        <v>348</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>344</v>
+      </c>
+      <c r="B34" t="s">
+        <v>350</v>
+      </c>
+      <c r="C34" t="s">
+        <v>351</v>
+      </c>
+      <c r="D34" t="s">
+        <v>202</v>
+      </c>
+      <c r="E34" t="s">
+        <v>352</v>
+      </c>
+      <c r="F34" t="s">
+        <v>353</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" t="s">
+        <v>355</v>
+      </c>
+      <c r="C35" t="s">
+        <v>256</v>
+      </c>
+      <c r="D35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" t="s">
+        <v>356</v>
+      </c>
+      <c r="F35" t="s">
+        <v>209</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>358</v>
+      </c>
+      <c r="B36" t="s">
+        <v>359</v>
+      </c>
+      <c r="C36" t="s">
+        <v>207</v>
+      </c>
+      <c r="D36" t="s">
+        <v>202</v>
+      </c>
+      <c r="E36" t="s">
+        <v>360</v>
+      </c>
+      <c r="F36" t="s">
+        <v>361</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>363</v>
+      </c>
+      <c r="B37" t="s">
+        <v>364</v>
+      </c>
+      <c r="C37" t="s">
+        <v>365</v>
+      </c>
+      <c r="D37" t="s">
+        <v>304</v>
+      </c>
+      <c r="E37" t="s">
+        <v>366</v>
+      </c>
+      <c r="F37" t="s">
+        <v>367</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>369</v>
+      </c>
+      <c r="B38" t="s">
+        <v>370</v>
+      </c>
+      <c r="C38" t="s">
+        <v>207</v>
+      </c>
+      <c r="D38" t="s">
+        <v>262</v>
+      </c>
+      <c r="E38" t="s">
+        <v>371</v>
+      </c>
+      <c r="F38" t="s">
+        <v>372</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>374</v>
+      </c>
+      <c r="B39" t="s">
+        <v>375</v>
+      </c>
+      <c r="C39" t="s">
+        <v>376</v>
+      </c>
+      <c r="D39" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" t="s">
+        <v>377</v>
+      </c>
+      <c r="F39" t="s">
+        <v>378</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>380</v>
+      </c>
+      <c r="B40" t="s">
+        <v>381</v>
+      </c>
+      <c r="C40" t="s">
+        <v>213</v>
+      </c>
+      <c r="D40" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" t="s">
+        <v>382</v>
+      </c>
+      <c r="F40" t="s">
+        <v>383</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>385</v>
+      </c>
+      <c r="B41" t="s">
+        <v>386</v>
+      </c>
+      <c r="C41" t="s">
+        <v>387</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
+        <v>360</v>
+      </c>
+      <c r="F41" t="s">
+        <v>388</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>390</v>
+      </c>
+      <c r="B42" t="s">
+        <v>391</v>
+      </c>
+      <c r="C42" t="s">
+        <v>219</v>
+      </c>
+      <c r="D42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" t="s">
+        <v>392</v>
+      </c>
+      <c r="F42" t="s">
+        <v>393</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>395</v>
+      </c>
+      <c r="B43" t="s">
+        <v>224</v>
+      </c>
+      <c r="C43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D43" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" t="s">
+        <v>272</v>
+      </c>
+      <c r="F43" t="s">
+        <v>227</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>395</v>
+      </c>
+      <c r="B44" t="s">
+        <v>224</v>
+      </c>
+      <c r="C44" t="s">
+        <v>229</v>
+      </c>
+      <c r="D44" t="s">
+        <v>202</v>
+      </c>
+      <c r="E44" t="s">
+        <v>272</v>
+      </c>
+      <c r="F44" t="s">
+        <v>227</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>398</v>
+      </c>
+      <c r="B45" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" t="s">
+        <v>202</v>
+      </c>
+      <c r="E45" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45" t="s">
+        <v>399</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>401</v>
+      </c>
+      <c r="B46" t="s">
+        <v>241</v>
+      </c>
+      <c r="C46" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" t="s">
+        <v>402</v>
+      </c>
+      <c r="F46" t="s">
+        <v>209</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>404</v>
+      </c>
+      <c r="B47" t="s">
+        <v>405</v>
+      </c>
+      <c r="C47" t="s">
+        <v>236</v>
+      </c>
+      <c r="D47" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" t="s">
+        <v>406</v>
+      </c>
+      <c r="F47" t="s">
+        <v>407</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>409</v>
+      </c>
+      <c r="B48" t="s">
+        <v>410</v>
+      </c>
+      <c r="C48" t="s">
+        <v>411</v>
+      </c>
+      <c r="D48" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" t="s">
+        <v>226</v>
+      </c>
+      <c r="F48" t="s">
+        <v>412</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>414</v>
+      </c>
+      <c r="B49" t="s">
+        <v>415</v>
+      </c>
+      <c r="C49" t="s">
+        <v>416</v>
+      </c>
+      <c r="D49" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" t="s">
+        <v>417</v>
+      </c>
+      <c r="F49" t="s">
+        <v>299</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B50" t="s">
+        <v>420</v>
+      </c>
+      <c r="C50" t="s">
+        <v>207</v>
+      </c>
+      <c r="D50" t="s">
+        <v>202</v>
+      </c>
+      <c r="E50" t="s">
+        <v>421</v>
+      </c>
+      <c r="F50" t="s">
+        <v>422</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>424</v>
+      </c>
+      <c r="B51" t="s">
+        <v>425</v>
+      </c>
+      <c r="C51" t="s">
+        <v>256</v>
+      </c>
+      <c r="D51" t="s">
+        <v>426</v>
+      </c>
+      <c r="E51" t="s">
+        <v>427</v>
+      </c>
+      <c r="F51" t="s">
+        <v>428</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>430</v>
+      </c>
+      <c r="B52" t="s">
+        <v>431</v>
+      </c>
+      <c r="C52" t="s">
+        <v>236</v>
+      </c>
+      <c r="D52" t="s">
+        <v>304</v>
+      </c>
+      <c r="E52" t="s">
+        <v>432</v>
+      </c>
+      <c r="F52" t="s">
+        <v>209</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>434</v>
+      </c>
+      <c r="B53" t="s">
+        <v>431</v>
+      </c>
+      <c r="C53" t="s">
+        <v>236</v>
+      </c>
+      <c r="D53" t="s">
+        <v>304</v>
+      </c>
+      <c r="E53" t="s">
+        <v>435</v>
+      </c>
+      <c r="F53" t="s">
+        <v>436</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>438</v>
+      </c>
+      <c r="B54" t="s">
+        <v>439</v>
+      </c>
+      <c r="C54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D54" t="s">
+        <v>202</v>
+      </c>
+      <c r="E54" t="s">
+        <v>209</v>
+      </c>
+      <c r="F54" t="s">
+        <v>441</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>443</v>
+      </c>
+      <c r="B55" t="s">
+        <v>241</v>
+      </c>
+      <c r="C55" t="s">
+        <v>213</v>
+      </c>
+      <c r="D55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E55" t="s">
+        <v>444</v>
+      </c>
+      <c r="F55" t="s">
+        <v>209</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>446</v>
+      </c>
+      <c r="B56" t="s">
+        <v>447</v>
+      </c>
+      <c r="C56" t="s">
+        <v>448</v>
+      </c>
+      <c r="D56" t="s">
+        <v>202</v>
+      </c>
+      <c r="E56" t="s">
+        <v>449</v>
+      </c>
+      <c r="F56" t="s">
+        <v>209</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>451</v>
+      </c>
+      <c r="B57" t="s">
+        <v>447</v>
+      </c>
+      <c r="C57" t="s">
+        <v>448</v>
+      </c>
+      <c r="D57" t="s">
+        <v>202</v>
+      </c>
+      <c r="E57" t="s">
+        <v>209</v>
+      </c>
+      <c r="F57" t="s">
+        <v>452</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>454</v>
+      </c>
+      <c r="B58" t="s">
+        <v>455</v>
+      </c>
+      <c r="C58" t="s">
+        <v>456</v>
+      </c>
+      <c r="D58" t="s">
+        <v>202</v>
+      </c>
+      <c r="E58" t="s">
+        <v>457</v>
+      </c>
+      <c r="F58" t="s">
+        <v>458</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>460</v>
+      </c>
+      <c r="B59" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" t="s">
+        <v>225</v>
+      </c>
+      <c r="D59" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" t="s">
+        <v>461</v>
+      </c>
+      <c r="F59" t="s">
+        <v>227</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>460</v>
+      </c>
+      <c r="B60" t="s">
+        <v>224</v>
+      </c>
+      <c r="C60" t="s">
+        <v>229</v>
+      </c>
+      <c r="D60" t="s">
+        <v>202</v>
+      </c>
+      <c r="E60" t="s">
+        <v>461</v>
+      </c>
+      <c r="F60" t="s">
+        <v>227</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>464</v>
+      </c>
+      <c r="B61" t="s">
+        <v>465</v>
+      </c>
+      <c r="C61" t="s">
+        <v>448</v>
+      </c>
+      <c r="D61" t="s">
+        <v>202</v>
+      </c>
+      <c r="E61" t="s">
+        <v>209</v>
+      </c>
+      <c r="F61" t="s">
+        <v>399</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>467</v>
+      </c>
+      <c r="B62" t="s">
+        <v>468</v>
+      </c>
+      <c r="C62" t="s">
+        <v>219</v>
+      </c>
+      <c r="D62" t="s">
+        <v>202</v>
+      </c>
+      <c r="E62" t="s">
+        <v>469</v>
+      </c>
+      <c r="F62" t="s">
+        <v>470</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>472</v>
+      </c>
+      <c r="B63" t="s">
+        <v>447</v>
+      </c>
+      <c r="C63" t="s">
+        <v>448</v>
+      </c>
+      <c r="D63" t="s">
+        <v>202</v>
+      </c>
+      <c r="E63" t="s">
+        <v>209</v>
+      </c>
+      <c r="F63" t="s">
+        <v>452</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>474</v>
+      </c>
+      <c r="B64" t="s">
+        <v>475</v>
+      </c>
+      <c r="C64" t="s">
+        <v>207</v>
+      </c>
+      <c r="D64" t="s">
+        <v>202</v>
+      </c>
+      <c r="E64" t="s">
+        <v>476</v>
+      </c>
+      <c r="F64" t="s">
+        <v>477</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>479</v>
+      </c>
+      <c r="B65" t="s">
+        <v>480</v>
+      </c>
+      <c r="C65" t="s">
+        <v>219</v>
+      </c>
+      <c r="D65" t="s">
+        <v>202</v>
+      </c>
+      <c r="E65" t="s">
+        <v>481</v>
+      </c>
+      <c r="F65" t="s">
+        <v>482</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>484</v>
+      </c>
+      <c r="B66" t="s">
+        <v>485</v>
+      </c>
+      <c r="C66" t="s">
+        <v>486</v>
+      </c>
+      <c r="D66" t="s">
+        <v>304</v>
+      </c>
+      <c r="E66" t="s">
+        <v>487</v>
+      </c>
+      <c r="F66" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>489</v>
+      </c>
+      <c r="B67" t="s">
+        <v>431</v>
+      </c>
+      <c r="C67" t="s">
+        <v>236</v>
+      </c>
+      <c r="D67" t="s">
+        <v>304</v>
+      </c>
+      <c r="E67" t="s">
+        <v>490</v>
+      </c>
+      <c r="F67" t="s">
+        <v>209</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>492</v>
+      </c>
+      <c r="B68" t="s">
+        <v>493</v>
+      </c>
+      <c r="C68" t="s">
+        <v>494</v>
+      </c>
+      <c r="D68" t="s">
+        <v>202</v>
+      </c>
+      <c r="E68" t="s">
+        <v>495</v>
+      </c>
+      <c r="F68" t="s">
+        <v>496</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>498</v>
+      </c>
+      <c r="B69" t="s">
+        <v>499</v>
+      </c>
+      <c r="C69" t="s">
+        <v>500</v>
+      </c>
+      <c r="D69" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69" t="s">
+        <v>209</v>
+      </c>
+      <c r="F69" t="s">
+        <v>299</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>502</v>
+      </c>
+      <c r="B70" t="s">
+        <v>503</v>
+      </c>
+      <c r="C70" t="s">
+        <v>207</v>
+      </c>
+      <c r="D70" t="s">
+        <v>202</v>
+      </c>
+      <c r="E70" t="s">
+        <v>504</v>
+      </c>
+      <c r="F70" t="s">
+        <v>204</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>506</v>
+      </c>
+      <c r="B71" t="s">
+        <v>507</v>
+      </c>
+      <c r="C71" t="s">
+        <v>207</v>
+      </c>
+      <c r="D71" t="s">
+        <v>202</v>
+      </c>
+      <c r="E71" t="s">
+        <v>209</v>
+      </c>
+      <c r="F71" t="s">
+        <v>508</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>510</v>
+      </c>
+      <c r="B72" t="s">
+        <v>511</v>
+      </c>
+      <c r="C72" t="s">
+        <v>213</v>
+      </c>
+      <c r="D72" t="s">
+        <v>262</v>
+      </c>
+      <c r="E72" t="s">
+        <v>512</v>
+      </c>
+      <c r="F72" t="s">
+        <v>513</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>515</v>
+      </c>
+      <c r="B73" t="s">
+        <v>516</v>
+      </c>
+      <c r="C73" t="s">
+        <v>207</v>
+      </c>
+      <c r="D73" t="s">
+        <v>202</v>
+      </c>
+      <c r="E73" t="s">
+        <v>517</v>
+      </c>
+      <c r="F73" t="s">
+        <v>518</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>520</v>
+      </c>
+      <c r="B74" t="s">
+        <v>521</v>
+      </c>
+      <c r="C74" t="s">
+        <v>213</v>
+      </c>
+      <c r="D74" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" t="s">
+        <v>522</v>
+      </c>
+      <c r="F74" t="s">
+        <v>523</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-04.xlsx
+++ b/docs/xlsx/jobs-2026-09-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="872">
   <si>
     <t>Title</t>
   </si>
@@ -613,6 +613,42 @@
     <t>https://www.conservationjobboard.com/job-listing-youth-programs-coordinator-waitsfield-vermont/8065866759</t>
   </si>
   <si>
+    <t>ADA/504 Coordinator</t>
+  </si>
+  <si>
+    <t>Santa Clara University</t>
+  </si>
+  <si>
+    <t>Santa Clara, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7db377ead1ee4fb8b255754a0ce03ce1-ada504-coordinator-santa-clara-university-santa-clara</t>
+  </si>
+  <si>
+    <t>Advancement Associate</t>
+  </si>
+  <si>
+    <t>Mount Tamalpais College</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b21165c7134478ea220cf194eb07fea-advancement-associate-mount-tamalpais-college-san-rafael</t>
+  </si>
+  <si>
     <t>Assistant Attorney General: Affirmative Litigation (3910)</t>
   </si>
   <si>
@@ -622,9 +658,6 @@
     <t>Utica, New York</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 87594.00 - 186493.00/year</t>
   </si>
   <si>
@@ -643,9 +676,6 @@
     <t>USD 90356.00 - 190493.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/government-job/8276ba9724374e97aee1293751dc5941-assistant-attorney-general-civil-litigation-for-nys-3909-new-york-state-office-of-the-attorney-general-new-york</t>
   </si>
   <si>
@@ -748,6 +778,27 @@
     <t>https://www.idealist.org/en/job/a1e8ac1e2c894e47acfd44871f74a2fe-associate-culture-sports-meridian-international-center-washington</t>
   </si>
   <si>
+    <t>Meridian International</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a1e8ac1e2c894e47acfd44871f74a2fe-associate-culture-sports-meridian-international-washington</t>
+  </si>
+  <si>
+    <t>Bilingual Organizer Spanish/English</t>
+  </si>
+  <si>
+    <t>Workers United, New York New Jersey Regional Joint Board, a/w SEIU</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Race Ethnicity, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b2541fb699647088ce7e14f9e4eb7a4-bilingual-organizer-spanishenglish-workers-united-new-york-new-jersey-regional-joint-board-aw-seiu-new-york</t>
+  </si>
+  <si>
     <t>Bilingual Paralegal - Social Security Income (SSI)</t>
   </si>
   <si>
@@ -763,6 +814,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/b32c14c6f5154cb5a3bce7900e006e59-bilingual-paralegal-social-security-income-ssi-legal-services-of-new-jersey-edison</t>
   </si>
   <si>
+    <t>California Communications Associate</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/523c3314a04b4a19b95dbf72b5221e6b-california-communications-associate-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Case Management Supervisor-Esperanza Immigrant Rights Project</t>
+  </si>
+  <si>
+    <t>Catholic Charities of Los Angeles, Inc</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 76777.00/year</t>
+  </si>
+  <si>
+    <t>Education, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6a0693d7ace43aa92dd58993b2c0442-case-management-supervisor-esperanza-immigrant-rights-project-catholic-charities-of-los-angeles-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>Case Manager II- Bilingual in Farsi and Dari</t>
+  </si>
+  <si>
+    <t>Neighborhood House</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 31.48 - 34.90/hour</t>
+  </si>
+  <si>
+    <t>Education, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06ef5cdec2ae41549ad22c750b543361-case-manager-ii-bilingual-in-farsi-and-dari-neighborhood-house-seattle</t>
+  </si>
+  <si>
     <t>Certified Nursing Assistant</t>
   </si>
   <si>
@@ -796,6 +898,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/06d25b4d01814c4ea6414c3be4fdaa97-chief-financial-and-operations-officer-landesa-seattle</t>
   </si>
   <si>
+    <t>Chief of Staff</t>
+  </si>
+  <si>
+    <t>Civilization Research Institute</t>
+  </si>
+  <si>
+    <t>Asheville, North Carolina</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/803d2823705c4fd7b3bc6250ea43a0fe-chief-of-staff-civilization-research-institute-asheville</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Play Rugby, Inc.</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/856bcf51c4b24b7a96ff985e6a8bb4bb-chief-operating-officer-play-rugby-inc-new-york</t>
+  </si>
+  <si>
+    <t>Civic Learning Program Manager</t>
+  </si>
+  <si>
+    <t>League of Women Voters of Washington</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37aa8f98bbe348f7818ca932589c13b7-civic-learning-program-manager-league-of-women-voters-of-washington-seattle</t>
+  </si>
+  <si>
     <t>Client Navigator</t>
   </si>
   <si>
@@ -829,6 +982,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0f17298a124e4964b60709192a253550-client-services-coordinator-shine-foundation-inc-new-york</t>
   </si>
   <si>
+    <t>Communication Manager</t>
+  </si>
+  <si>
+    <t>Animal Aid Unlimited</t>
+  </si>
+  <si>
+    <t>Udaipur, Rajasthan, IN</t>
+  </si>
+  <si>
+    <t>INR 75000.00 - 110000.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57e58d10638d4a3c9ae4544c667db624-communication-manager-animal-aid-unlimited-udaipur</t>
+  </si>
+  <si>
     <t>Communications Manager</t>
   </si>
   <si>
@@ -856,21 +1027,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/1be599308e9345678624475c03236b96-communications-manager-america-saves-consumer-federation-of-america-washington</t>
   </si>
   <si>
+    <t>Communications Support Specialist</t>
+  </si>
+  <si>
+    <t>Cheshire Law Group</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/835070cd2a974c848187906257da438e-communications-support-specialist-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
     <t>Global Arts Live</t>
   </si>
   <si>
     <t>Cambridge, MA</t>
   </si>
   <si>
-    <t>USD 70000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>Arts Music</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/1bcfd3ec02cc4be7bf1c472b3da43f72-community-engagement-manager-global-arts-live-cambridge</t>
   </si>
   <si>
+    <t>Community Network Anchor Program Coordinator — Independent Contractor</t>
+  </si>
+  <si>
+    <t>NAMI Illinois</t>
+  </si>
+  <si>
+    <t>Remote (Illinois)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Communications Access, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/034d7213e5ed40e9ba6c80ed999c4c49-community-network-anchor-program-coordinator-independent-contractor-nami-illinois-chicago</t>
+  </si>
+  <si>
     <t>Community Organizer</t>
   </si>
   <si>
@@ -919,6 +1123,66 @@
     <t>https://www.idealist.org/en/job/0b60d36d1bb145f3a46a035d30526c39-coordinator-academic-advising-marist-university-poughkeepsie</t>
   </si>
   <si>
+    <t>Criminal Defense Practice Social Worker</t>
+  </si>
+  <si>
+    <t>The Bronx Defenders</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 87177.00 - 114577.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a0c72277003460bbb116d0f9a3a17e0-criminal-defense-practice-social-worker-the-bronx-defenders-bronx-county</t>
+  </si>
+  <si>
+    <t>Data and Research Analyst</t>
+  </si>
+  <si>
+    <t>Vermont Care Partners</t>
+  </si>
+  <si>
+    <t>Montpelier, Vermont</t>
+  </si>
+  <si>
+    <t>USD 90000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ee5b0d4386d4f7688fbe33d4a9708ea-data-and-research-analyst-vermont-care-partners-montpelier</t>
+  </si>
+  <si>
+    <t>Development &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>Savanna Institute</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b12c10847b64a6cb1968edba4c1f010-development-communications-manager-savanna-institute-madison</t>
+  </si>
+  <si>
+    <t>Development Associate, Special Events at Lincoln Center Theater</t>
+  </si>
+  <si>
+    <t>Lincoln Center Theater - New York</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2266ff3ed0a34bca984594f4e60a41fb-development-associate-special-events-at-lincoln-center-theater-lincoln-center-theater-new-york-new-york</t>
+  </si>
+  <si>
     <t>Development Coordinator</t>
   </si>
   <si>
@@ -928,9 +1192,6 @@
     <t>Beacon, New York</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 23.00 - 24.00/hour</t>
   </si>
   <si>
@@ -982,6 +1243,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b9e92eef18fb40e8af63a08c0d2ab190-development-director-los-angeles-lift-los-angeles</t>
   </si>
   <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>The Henry L. Stimson Center</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 137000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cfa60ee0ec344ae5a216de7aa5afe75d-director-of-communications-the-henry-l-stimson-center-washington</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
@@ -997,6 +1273,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/6e225033477b4430b18dfd4864cdde73-director-of-development-pike-place-market-foundation-seattle</t>
   </si>
   <si>
+    <t>America's Automotive Trust and LeMay - America's Car Museum</t>
+  </si>
+  <si>
+    <t>Tacoma, Washington</t>
+  </si>
+  <si>
+    <t>USD 111368.88 - 138981.85/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01db72fee06d4421bddd3df9997cd866-director-of-development-americas-automotive-trust-and-lemay-americas-car-museum-tacoma</t>
+  </si>
+  <si>
     <t>Director of Facilities</t>
   </si>
   <si>
@@ -1033,21 +1324,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/3228a8f2fcf34f8d83b492c908554966-director-of-finance-and-operations-wolf-performing-arts-center-bryn-mawr</t>
   </si>
   <si>
+    <t>Domestic Violence Response Team Coordinator</t>
+  </si>
+  <si>
+    <t>Women Aware, Inc.</t>
+  </si>
+  <si>
+    <t>New Brunswick, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59138346ffb84733a73e380b57000c9f-domestic-violence-response-team-coordinator-women-aware-inc-new-brunswick</t>
+  </si>
+  <si>
+    <t>Employer Partnerships Lead</t>
+  </si>
+  <si>
+    <t>PowerCorpsPHL</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/89fc2ce823d744bd93a65a701bd8b2a4-employer-partnerships-lead-powercorpsphl-philadelphia</t>
+  </si>
+  <si>
     <t>Executive Assistant</t>
   </si>
   <si>
     <t>Grassroots Global Justice</t>
   </si>
   <si>
-    <t>Washington, DC</t>
-  </si>
-  <si>
     <t>USD 63800.00 - 76975.00/year</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/job/7df0173e750a44e2bb41363243791501-executive-assistant-grassroots-global-justice-washington</t>
   </si>
   <si>
+    <t>Executive Assistant to the President &amp; CEO</t>
+  </si>
+  <si>
+    <t>Institute of International Education</t>
+  </si>
+  <si>
+    <t>USD 90508.00 - 107319.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b2f20392f4da413ba88e894ba6a8182b-executive-assistant-to-the-president-ceo-institute-of-international-education-washington</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -1090,21 +1420,132 @@
     <t>https://www.idealist.org/en/job/11c2a2dad3df4bf2b2f760958bde1c6f-executive-director-pacific-hospital-preservation-development-authority-phpda-seattle</t>
   </si>
   <si>
+    <t>Brazos Valley Food Bank, Inc.</t>
+  </si>
+  <si>
+    <t>Bryan, Texas</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd3332b14f534924b8d863f1ade00b19-executive-director-brazos-valley-food-bank-inc-bryan</t>
+  </si>
+  <si>
+    <t>Executive Vice President of Program Operations</t>
+  </si>
+  <si>
+    <t>Anthos Home</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f92e197cd0b4f6d8b33fdc48883b1b9-executive-vice-president-of-program-operations-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Extreme Kids &amp;amp; Crew - Youth Program Facilitator</t>
+  </si>
+  <si>
+    <t>Extreme Kids and Crew</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3af2a96c3e94469f95d39c9dbafc0dd1-extreme-kids-amp-crew-youth-program-facilitator-extreme-kids-and-crew-new-york</t>
+  </si>
+  <si>
+    <t>Faculty Position in Data Science and Society, Open Rank</t>
+  </si>
+  <si>
+    <t>Georgetown University</t>
+  </si>
+  <si>
+    <t>Doha, Qatar</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/79fd90c6257b46e3b001f8d7caa96331-faculty-position-in-data-science-and-society-open-rank-georgetown-university-doha</t>
+  </si>
+  <si>
+    <t>Faculty Position in Health and Environment, Open Rank</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c37da441fc0b4bc890aecc4ee40535c7-faculty-position-in-health-and-environment-open-rank-georgetown-university-doha</t>
+  </si>
+  <si>
+    <t>Faculty Position in Philosophy, Open Rank</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1b1be64adf7f46e9bd564c93d8e42df2-faculty-position-in-philosophy-open-rank-georgetown-university-doha</t>
+  </si>
+  <si>
+    <t>Family Law Attorney</t>
+  </si>
+  <si>
+    <t>Saahas for Cause</t>
+  </si>
+  <si>
+    <t>Artesia, California</t>
+  </si>
+  <si>
+    <t>USD 41.00 - 44.00/day</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1dcd5dab82241c68954ae53ee117ad5-family-law-attorney-saahas-for-cause-artesia</t>
+  </si>
+  <si>
+    <t>Finance &amp; Administration Specialist</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/437ce29145e8432eb9badbc0fba1886a-finance-administration-specialist-anthos-home-new-york</t>
+  </si>
+  <si>
     <t>Finance and Operations Administrator</t>
   </si>
   <si>
     <t>Asian Cultural Council</t>
   </si>
   <si>
-    <t>USD 65000.00 - 70000.00/year</t>
-  </si>
-  <si>
     <t>Arts Music, International Relations</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/12297560260a46bd9d9e82ab7a880c30-finance-and-operations-administrator-asian-cultural-council-new-york</t>
   </si>
   <si>
+    <t>Finance Executive Director</t>
+  </si>
+  <si>
+    <t>Samish Indian Nation</t>
+  </si>
+  <si>
+    <t>Anacortes, Washington</t>
+  </si>
+  <si>
+    <t>USD 63356.80 - 118040.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a5011220d0743db84cb45a4d6f590d2-finance-executive-director-samish-indian-nation-anacortes</t>
+  </si>
+  <si>
     <t>Food Pantry Coordinator</t>
   </si>
   <si>
@@ -1171,6 +1612,144 @@
     <t>https://www.idealist.org/en/nonprofit-job/e2783ae27e51455a8920ac49f2d9b2ad-government-relations-director-network-lobby-for-catholic-social-justice-washington</t>
   </si>
   <si>
+    <t>Grant Writer &amp; Manager</t>
+  </si>
+  <si>
+    <t>The Honeycomb Project</t>
+  </si>
+  <si>
+    <t>Remote (Chicago, Illinois)</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7cd2645c6dfe4a9e91b47f60923d2f66-grant-writer-manager-the-honeycomb-project-chicago</t>
+  </si>
+  <si>
+    <t>Green Corps Campaigner</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 44450.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/feee89d205444d4e9d796c40f24150e3-green-corps-campaigner-green-corps-phoenix</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac16bb6dada04596aa9f86e10704fe1e-green-corps-campaigner-green-corps-kansas-city</t>
+  </si>
+  <si>
+    <t>Charleston, South Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aac0dcd67dd345f895d08793904ab855-green-corps-campaigner-green-corps-charleston</t>
+  </si>
+  <si>
+    <t>Indianapolis, Indiana</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9fd73b06a24f40ef975bbc5db9809e10-green-corps-campaigner-green-corps-indianapolis</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f1741de322147f1878cf34aa7dce25e-green-corps-campaigner-green-corps-albuquerque</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f68ed50e8e748838886ca76092ec62f-green-corps-campaigner-green-corps-chicago</t>
+  </si>
+  <si>
+    <t>Nashville, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75fd2e87f2544f1bba7641a981a7c563-green-corps-campaigner-green-corps-nashville</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fe872bac02a4c24bb717620250afedb-green-corps-campaigner-green-corps-miami</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e78ca9b2df340a68893d2d762ad37a9-green-corps-campaigner-green-corps-richmond</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef5ee5f8730d4f729ed7db9a5c89a697-green-corps-campaigner-green-corps-washington</t>
+  </si>
+  <si>
+    <t>Tampa, Florida</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdfffb0518c54475a40bd3d430becb0a-green-corps-campaigner-green-corps-tampa</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bacfe02e59264acf93cc66a2986b26ca-green-corps-campaigner-green-corps-houston</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8cae44f507643caac77f31cc69b0f16-green-corps-campaigner-green-corps-detroit</t>
+  </si>
+  <si>
+    <t>Charlotte, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b019a03f4284411188ecb843091dd8fe-green-corps-campaigner-green-corps-charlotte</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa7e0b205d2a477c9c58960efa52dd45-green-corps-campaigner-green-corps-minneapolis</t>
+  </si>
+  <si>
+    <t>Milwaukee, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d1df903702d4602a45c77ae10b0f24d-green-corps-campaigner-green-corps-milwaukee</t>
+  </si>
+  <si>
+    <t>Cincinnati, Ohio</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fca9ff464e346909358db6b15d1ad53-green-corps-campaigner-green-corps-cincinnati</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/522b8799a2144f089717db1f1496d2ce-green-corps-campaigner-green-corps-baltimore</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/000cce5740f34b31828d54c714268de8-green-corps-campaigner-green-corps-portland</t>
+  </si>
+  <si>
     <t>GreenWorks Director</t>
   </si>
   <si>
@@ -1228,6 +1807,9 @@
     <t>https://www.idealist.org/en/job/8fa2503a86d9449dbec84c677968be85-houseman-steward-events-meridian-international-center-washington</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/job/8fa2503a86d9449dbec84c677968be85-houseman-steward-events-meridian-international-washington</t>
+  </si>
+  <si>
     <t>HR &amp; Office Administration Coordinator</t>
   </si>
   <si>
@@ -1243,6 +1825,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/2dbac2a8aa754ee6829380d26372981e-hr-office-administration-coordinator-opus-dance-theatre-and-community-services-inc-kings-county</t>
   </si>
   <si>
+    <t>Human Resources Business Partner</t>
+  </si>
+  <si>
+    <t>Henry Art Gallery</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d61ae9a95d634303b9dd417d57aa0ff7-human-resources-business-partner-henry-art-gallery-seattle</t>
+  </si>
+  <si>
     <t>Human Resources Director</t>
   </si>
   <si>
@@ -1258,6 +1849,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b2d2c6ade579466785a248517230b7f9-human-resources-director-mennonite-central-committee-akron</t>
   </si>
   <si>
+    <t>Immigration Attorney</t>
+  </si>
+  <si>
+    <t>Worker Justice Center of New York, Inc.</t>
+  </si>
+  <si>
+    <t>Rochester, NY</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 93500.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6bb9d1fcbd448728bc671f4691579eb-immigration-attorney-worker-justice-center-of-new-york-inc-rochester</t>
+  </si>
+  <si>
     <t>Instructor or Assistant Professor - Library</t>
   </si>
   <si>
@@ -1273,6 +1882,99 @@
     <t>https://www.idealist.org/en/job/58aa6a6151c1487f90175894a2afec81-instructor-or-assistant-professor-library-laguardia-community-college-queens-county</t>
   </si>
   <si>
+    <t>JOIN A PROGRESSIVE CAMPAIGN IN LA!</t>
+  </si>
+  <si>
+    <t>UNITE HERE! Local 11</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec4b4e34f96c41cc88e636c7c6fcc3ef-join-a-progressive-campaign-in-la-unite-here-local-11-los-angeles</t>
+  </si>
+  <si>
+    <t>Lead Diversion Facilitator &amp; Youth Support Coordinator</t>
+  </si>
+  <si>
+    <t>Beyond the Bars</t>
+  </si>
+  <si>
+    <t>USD 45240.00 - 45240.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12082ebfab104d7f9fa54f7cde0f3742-lead-diversion-facilitator-youth-support-coordinator-beyond-the-bars-philadelphia</t>
+  </si>
+  <si>
+    <t>Make Textbooks Affordable Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28fdcda5ccda42ecafbf7f9b67409420-make-textbooks-affordable-organizer-student-pirgs-washington</t>
+  </si>
+  <si>
+    <t>Managing Research Scientist, EOD</t>
+  </si>
+  <si>
+    <t>The Institute for Health Metrics and Evaluation</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 143820.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d2140bc5dce4ad4a1552ac2891e109f-managing-research-scientist-eod-the-institute-for-health-metrics-and-evaluation-seattle</t>
+  </si>
+  <si>
+    <t>Marine Science Storytelling Fellow</t>
+  </si>
+  <si>
+    <t>STEAM the Streets</t>
+  </si>
+  <si>
+    <t>Woods Hole, Massachusetts</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/184a39fe94894346929278d539d5b7fd-marine-science-storytelling-fellow-steam-the-streets-woods-hole</t>
+  </si>
+  <si>
+    <t>NCCER Core Lead Instructor</t>
+  </si>
+  <si>
+    <t>Montgomery County OIC</t>
+  </si>
+  <si>
+    <t>Norristown, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19b208bb98d54d50ad03f900bc6747d9-nccer-core-lead-instructor-montgomery-county-oic-norristown</t>
+  </si>
+  <si>
     <t>Non-Teaching Adjunct, Level 1 - Office of Institutional Advancement and Communications</t>
   </si>
   <si>
@@ -1288,15 +1990,60 @@
     <t>https://www.idealist.org/en/job/0310d6b3e00641bc98988818e163b58c-non-teaching-adjunct-level-1-office-of-institutional-advancement-and-communications-the-graduate-center-cuny-new-york</t>
   </si>
   <si>
+    <t>San Francisco Village</t>
+  </si>
+  <si>
+    <t>Community Development, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f720d88921a24c11b1572cacfafb5c57-office-manager-san-francisco-village-san-francisco</t>
+  </si>
+  <si>
+    <t>Pilsen Neighbors Community Council</t>
+  </si>
+  <si>
+    <t>USD 38000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Civic Engagement, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7998f5e7b21e47bf8f348e21cae519c3-office-manager-pilsen-neighbors-community-council-chicago</t>
+  </si>
+  <si>
+    <t>Paralegal – Housing</t>
+  </si>
+  <si>
+    <t>Counsel for Justice</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/549b1dbead2b4296bddf4e4f5c80e568-paralegal-housing-counsel-for-justice-los-angeles</t>
+  </si>
+  <si>
+    <t>Paralegal Manager-Esperanza Immigrant Rights Project</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 71500.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18f559040350464e9e61ec9f37c1876f-paralegal-manager-esperanza-immigrant-rights-project-catholic-charities-of-los-angeles-inc-los-angeles</t>
+  </si>
+  <si>
     <t>Part-Time Leadership Workshop Co-Facilitator</t>
   </si>
   <si>
     <t>OneWorld Now!</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 26.00 - 26.00/hour</t>
   </si>
   <si>
@@ -1324,12 +2071,111 @@
     <t>USD 55.00 - 60.00/hour</t>
   </si>
   <si>
-    <t>Immigrants Or Refugees, Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/668edc5c7db4447e9cf9bc7f72e9e65a-part-time-staff-attorney-arab-american-association-of-new-york-kings-county</t>
   </si>
   <si>
+    <t>Part-time Transportation Justice Organizer</t>
+  </si>
+  <si>
+    <t>Center for Latino Advocacy Resources &amp; Organizing (CLARO)</t>
+  </si>
+  <si>
+    <t>USD 31.25 - 31.25/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4276737d796149d58b223f30099b9248-part-time-transportation-justice-organizer-center-for-latino-advocacy-resources-organizing-claro-san-francisco</t>
+  </si>
+  <si>
+    <t>Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>Cascade Bicycle Club</t>
+  </si>
+  <si>
+    <t>USD 84066.00 - 126099.00/year</t>
+  </si>
+  <si>
+    <t>Education, Transportation, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f241ad89e9249cb967b53e1d31b27aa-philanthropy-officer-cascade-bicycle-club-seattle</t>
+  </si>
+  <si>
+    <t>Phone Bank In Person for a Progressive Campaign!</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f777264711340f5b44d60ac835ca2af-phone-bank-in-person-for-a-progressive-campaign-unite-here-local-11-los-angeles</t>
+  </si>
+  <si>
+    <t>Procurement &amp; Pantry Lead</t>
+  </si>
+  <si>
+    <t>Snoqualmie Valley Food Bank</t>
+  </si>
+  <si>
+    <t>North Bend, Washington</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Rural Areas, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad7ce730bdbc4b609a3bee0c4438a522-procurement-pantry-lead-snoqualmie-valley-food-bank-north-bend</t>
+  </si>
+  <si>
+    <t>Production Manager</t>
+  </si>
+  <si>
+    <t>Ballet Hispánico</t>
+  </si>
+  <si>
+    <t>USD 37.00 - 42.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afcc12c40ab5405ea1df3f60638c75bf-production-manager-ballet-hispanico-new-york</t>
+  </si>
+  <si>
+    <t>Program Coordinator, AI Initiative</t>
+  </si>
+  <si>
+    <t>Pulitzer Center on Crisis Reporting</t>
+  </si>
+  <si>
+    <t>USD 62000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c27250ab91c94d508f728150f61278f4-program-coordinator-ai-initiative-pulitzer-center-on-crisis-reporting-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Family Engagement</t>
+  </si>
+  <si>
+    <t>UnidosUS</t>
+  </si>
+  <si>
+    <t>USD 62400.00 - 65600.00/year</t>
+  </si>
+  <si>
+    <t>Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eba7257c38214a1ea78a90b6dc8e4d21-program-coordinator-family-engagement-unidosus-los-angeles</t>
+  </si>
+  <si>
     <t>Program Manager, Dallas</t>
   </si>
   <si>
@@ -1354,6 +2200,33 @@
     <t>https://www.idealist.org/en/job/04c2be85a5ee420b962250228c6766bb-program-officer-sports-meridian-international-center-washington</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/job/04c2be85a5ee420b962250228c6766bb-program-officer-sports-meridian-international-washington</t>
+  </si>
+  <si>
+    <t>Program Operations Specialist</t>
+  </si>
+  <si>
+    <t>The Non-GMO Project</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5423d7178e574c079fd379103c408733-program-operations-specialist-the-non-gmo-project-bellingham</t>
+  </si>
+  <si>
+    <t>Psicólogo/a para nuestra sede del barrio La Teja (Pontevedra, Merlo)</t>
+  </si>
+  <si>
+    <t>Fundación Franciscana</t>
+  </si>
+  <si>
+    <t>Merlo, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Poverty, Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1040174e61d54596bf912061d2e16d08-psicologoa-para-nuestra-sede-del-barrio-la-teja-pontevedra-merlo-fundacion-franciscana-merlo</t>
+  </si>
+  <si>
     <t>Recruiting Specialist</t>
   </si>
   <si>
@@ -1378,6 +2251,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/df486db988f94838a8c9596a15d0d430-red-kettle-partners-director-the-salvation-army-national-headquarters-alexandria</t>
   </si>
   <si>
+    <t>Resource Connection Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e6b2b47b8854c4ca60c68f90de33519-resource-connection-coordinator-beyond-the-bars-philadelphia</t>
+  </si>
+  <si>
     <t>Restorative Practices Specialist</t>
   </si>
   <si>
@@ -1396,6 +2275,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/d0654e041bba44b3bb9406799bf251ea-restorative-practices-specialist-deep-center-savannah</t>
   </si>
   <si>
+    <t>Sales Representative</t>
+  </si>
+  <si>
+    <t>Together We Bake</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Poverty, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a844c86f4832408994a7e900c8eaa63b-sales-representative-together-we-bake-alexandria</t>
+  </si>
+  <si>
+    <t>Senior Attorney for Special Projects</t>
+  </si>
+  <si>
+    <t>Lawyers for Children America</t>
+  </si>
+  <si>
+    <t>Children Youth, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e41d053552a54b2ab881b0b0ffd25406-senior-attorney-for-special-projects-lawyers-for-children-america-miami</t>
+  </si>
+  <si>
     <t>Senior Community Organizer</t>
   </si>
   <si>
@@ -1453,6 +2359,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/c2326bdffc6d4c11848432b4462b2142-senior-director-of-strategic-communications-brand-and-marketing-grameen-america-inc-new-york</t>
   </si>
   <si>
+    <t>Senior Fellow and Director, North Africa, the Mediterranean, and the Sahel</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 234000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f09d4687ef8e441d83e9b873c833c7a5-senior-fellow-and-director-north-africa-the-mediterranean-and-the-sahel-the-henry-l-stimson-center-washington</t>
+  </si>
+  <si>
+    <t>Senior Legislative Associate</t>
+  </si>
+  <si>
+    <t>Southern Environmental Law Center</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 97350.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/689fec1d7c47417a9a4615a71947d26c-senior-legislative-associate-southern-environmental-law-center-washington</t>
+  </si>
+  <si>
+    <t>Senior Marketing Manager</t>
+  </si>
+  <si>
+    <t>Brownstone Surrogacy</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Reproductive Health Rights, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/2cc53562505948629b5a4c1c4cb8d007-senior-marketing-manager-brownstone-surrogacy-new-york</t>
+  </si>
+  <si>
     <t>Senior Product &amp; Project Manager - FieldKit</t>
   </si>
   <si>
@@ -1492,15 +2437,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/54654c94c4ab4f9291dca8666506bb52-social-services-case-worker-arab-american-association-of-new-york-kings-county</t>
   </si>
   <si>
+    <t>STAFF ATTORNEY- Baltimore County Workforce Development Project</t>
+  </si>
+  <si>
+    <t>Maryland Volunteer Lawyers Service</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/498b005bbc604ae8b67ced435931c2ee-staff-attorney-baltimore-county-workforce-development-project-maryland-volunteer-lawyers-service-baltimore</t>
+  </si>
+  <si>
+    <t>Staff Attorney-Esperanza Immigrant Rights Project</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aed144dbee9948b98e8c94448d882325-staff-attorney-esperanza-immigrant-rights-project-catholic-charities-of-los-angeles-inc-los-angeles</t>
+  </si>
+  <si>
     <t>Staff Attorney, Senior Staff Attorney, or Senior Counsel, Immigrants' Rights Project</t>
   </si>
   <si>
     <t>American Civil Liberties Union</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 96069.00 - 219104.00/year</t>
   </si>
   <si>
@@ -1510,6 +2473,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/a76198df2d4146b0aecbb6bd5431b09c-staff-attorney-senior-staff-attorney-or-senior-counsel-immigrants-rights-project-american-civil-liberties-union-san-francisco</t>
   </si>
   <si>
+    <t>Strategic Communications/PR Consultant</t>
+  </si>
+  <si>
+    <t>PFLAG National</t>
+  </si>
+  <si>
+    <t>Family, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66d0d044b9154686a4f4ca9f1841da3f-strategic-communicationspr-consultant-pflag-national-washington</t>
+  </si>
+  <si>
     <t>Strategic Initiatives Project Coordinator</t>
   </si>
   <si>
@@ -1522,6 +2497,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/05d17993529f4adc91ec6ad6817cfff8-strategic-initiatives-project-coordinator-kenyon-college-gambier</t>
   </si>
   <si>
+    <t>Student Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f16663fac2164729aa9d86eabe26e21e-student-coordinator-beyond-the-bars-philadelphia</t>
+  </si>
+  <si>
     <t>Supervising Financial Counselor</t>
   </si>
   <si>
@@ -1534,6 +2515,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/54887050dbf947faa68e34e3353ee720-supervising-financial-counselor-new-york-legal-assistance-group-nylag-new-york</t>
   </si>
   <si>
+    <t>Teaching Faculty Position in English and Writing, Open Rank</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ea573b9b11e94237b27430c0f4773195-teaching-faculty-position-in-english-and-writing-open-rank-georgetown-university-doha</t>
+  </si>
+  <si>
+    <t>Teaching Faculty Position in Instructional Arabic, Open Rank</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9ea6a67e5378401b8a14db561bb5c0ae-teaching-faculty-position-in-instructional-arabic-open-rank-georgetown-university-doha</t>
+  </si>
+  <si>
+    <t>Teaching Faculty Position in Instructional French, Open Rank</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d3bb0d9279314a0385850b07fb8e85fd-teaching-faculty-position-in-instructional-french-open-rank-georgetown-university-doha</t>
+  </si>
+  <si>
+    <t>Teaching Faculty Position in Mathematics, Open Rank</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0e0546e7ff164333b6333dcf595161f4-teaching-faculty-position-in-mathematics-open-rank-georgetown-university-doha</t>
+  </si>
+  <si>
+    <t>Temporary Staff Attorney – Housing</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01456c6ec4004a6a93e54f34cce9512e-temporary-staff-attorney-housing-counsel-for-justice-los-angeles</t>
+  </si>
+  <si>
     <t>Training Institute Manager</t>
   </si>
   <si>
@@ -1576,6 +2590,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/4d7d90053f3049b684998c572cf6db75-vice-president-of-communications-pure-earthblacksmith-institute-new-york</t>
   </si>
   <si>
+    <t>VP of Whole Child Education</t>
+  </si>
+  <si>
+    <t>Action4Equity</t>
+  </si>
+  <si>
+    <t>Winston-Salem, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39e47ec8fe9c467ab9b8562ba1a2ae42-vp-of-whole-child-education-action4equity-winston-salem</t>
+  </si>
+  <si>
     <t>Washington Director of External Engagement</t>
   </si>
   <si>
@@ -1589,6 +2621,15 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/9b718ab5c58f47438fcad857f47ac30c-washington-director-of-external-engagement-israel-policy-forum-washington</t>
+  </si>
+  <si>
+    <t>Worksite Organizer: Bilingual Spanish/English</t>
+  </si>
+  <si>
+    <t>Community Development, Immigrants Or Refugees, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b55a02e0cc345e6b5ac0497abd255b4-worksite-organizer-bilingual-spanishenglish-workers-united-new-york-new-jersey-regional-joint-board-aw-seiu-new-york</t>
   </si>
 </sst>
 </file>
@@ -2936,7 +3977,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2992,18 +4033,18 @@
         <v>203</v>
       </c>
       <c r="F2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" t="s">
         <v>206</v>
-      </c>
-      <c r="B3" t="s">
-        <v>200</v>
       </c>
       <c r="C3" t="s">
         <v>207</v>
@@ -3049,53 +4090,53 @@
         <v>217</v>
       </c>
       <c r="B5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" t="s">
         <v>218</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" t="s">
         <v>219</v>
       </c>
-      <c r="D5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="F5" t="s">
-        <v>221</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" t="s">
         <v>223</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" t="s">
         <v>224</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>225</v>
       </c>
-      <c r="D6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="H6" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="F6" t="s">
-        <v>227</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
         <v>229</v>
@@ -3104,102 +4145,102 @@
         <v>202</v>
       </c>
       <c r="E7" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C8" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D8" t="s">
         <v>202</v>
       </c>
       <c r="E8" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F8" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B9" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="D9" t="s">
         <v>202</v>
       </c>
       <c r="E9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F9" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B10" t="s">
         <v>234</v>
       </c>
-      <c r="B10" t="s">
-        <v>235</v>
-      </c>
       <c r="C10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" t="s">
         <v>236</v>
       </c>
-      <c r="D10" t="s">
-        <v>202</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>237</v>
       </c>
-      <c r="F10" t="s">
-        <v>238</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D11" t="s">
         <v>202</v>
       </c>
       <c r="E11" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F11" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>243</v>
@@ -3222,30 +4263,30 @@
         <v>247</v>
       </c>
       <c r="F12" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D13" t="s">
         <v>202</v>
       </c>
       <c r="E13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F13" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>253</v>
@@ -3253,519 +4294,519 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" t="s">
         <v>254</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" t="s">
+        <v>252</v>
+      </c>
+      <c r="F14" t="s">
+        <v>203</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="C14" t="s">
-        <v>256</v>
-      </c>
-      <c r="D14" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" t="s">
-        <v>257</v>
-      </c>
-      <c r="F14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C15" t="s">
+        <v>218</v>
+      </c>
+      <c r="D15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" t="s">
+        <v>258</v>
+      </c>
+      <c r="F15" t="s">
+        <v>259</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="B15" t="s">
-        <v>261</v>
-      </c>
-      <c r="C15" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" t="s">
-        <v>262</v>
-      </c>
-      <c r="E15" t="s">
-        <v>263</v>
-      </c>
-      <c r="F15" t="s">
-        <v>264</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B16" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C16" t="s">
-        <v>207</v>
+        <v>263</v>
       </c>
       <c r="D16" t="s">
         <v>202</v>
       </c>
       <c r="E16" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F16" t="s">
-        <v>269</v>
+        <v>215</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B17" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" t="s">
+        <v>269</v>
+      </c>
+      <c r="F17" t="s">
+        <v>270</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="B17" t="s">
-        <v>224</v>
-      </c>
-      <c r="C17" t="s">
-        <v>225</v>
-      </c>
-      <c r="D17" t="s">
-        <v>202</v>
-      </c>
-      <c r="E17" t="s">
-        <v>272</v>
-      </c>
-      <c r="F17" t="s">
-        <v>227</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B18" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D18" t="s">
         <v>202</v>
       </c>
       <c r="E18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F18" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C19" t="s">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="D19" t="s">
         <v>202</v>
       </c>
       <c r="E19" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>283</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C20" t="s">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="D20" t="s">
         <v>202</v>
       </c>
       <c r="E20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>289</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>290</v>
       </c>
       <c r="D21" t="s">
         <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F21" t="s">
-        <v>227</v>
+        <v>292</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B22" t="s">
-        <v>224</v>
+        <v>295</v>
       </c>
       <c r="C22" t="s">
-        <v>229</v>
+        <v>296</v>
       </c>
       <c r="D22" t="s">
         <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>286</v>
+        <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B23" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C23" t="s">
-        <v>291</v>
+        <v>218</v>
       </c>
       <c r="D23" t="s">
         <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F23" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B24" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C24" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="E24" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="F24" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B25" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s">
-        <v>303</v>
+        <v>218</v>
       </c>
       <c r="D25" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E25" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="F25" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B26" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D26" t="s">
         <v>202</v>
       </c>
       <c r="E26" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="F26" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B27" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="C27" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D27" t="s">
         <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="F27" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B28" t="s">
-        <v>318</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D28" t="s">
         <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="F28" t="s">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B29" t="s">
-        <v>323</v>
+        <v>234</v>
       </c>
       <c r="C29" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="D29" t="s">
         <v>202</v>
       </c>
       <c r="E29" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F29" t="s">
-        <v>325</v>
+        <v>237</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C30" t="s">
-        <v>329</v>
+        <v>223</v>
       </c>
       <c r="D30" t="s">
         <v>202</v>
       </c>
       <c r="E30" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F30" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B31" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C31" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D31" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="E31" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F31" t="s">
-        <v>337</v>
+        <v>215</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>339</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C32" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D32" t="s">
         <v>202</v>
       </c>
       <c r="E32" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="F32" t="s">
-        <v>209</v>
+        <v>344</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C33" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D33" t="s">
-        <v>304</v>
+        <v>349</v>
       </c>
       <c r="E33" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F33" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B34" t="s">
-        <v>350</v>
+        <v>234</v>
       </c>
       <c r="C34" t="s">
-        <v>351</v>
+        <v>235</v>
       </c>
       <c r="D34" t="s">
         <v>202</v>
       </c>
       <c r="E34" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F34" t="s">
-        <v>353</v>
+        <v>237</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B35" t="s">
-        <v>355</v>
+        <v>234</v>
       </c>
       <c r="C35" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="D35" t="s">
         <v>202</v>
       </c>
       <c r="E35" t="s">
+        <v>354</v>
+      </c>
+      <c r="F35" t="s">
+        <v>237</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="F35" t="s">
-        <v>209</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>357</v>
+      </c>
+      <c r="B36" t="s">
         <v>358</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>359</v>
-      </c>
-      <c r="C36" t="s">
-        <v>207</v>
       </c>
       <c r="D36" t="s">
         <v>202</v>
@@ -3791,7 +4832,7 @@
         <v>365</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="E37" t="s">
         <v>366</v>
@@ -3811,16 +4852,16 @@
         <v>370</v>
       </c>
       <c r="C38" t="s">
-        <v>207</v>
+        <v>371</v>
       </c>
       <c r="D38" t="s">
-        <v>262</v>
+        <v>202</v>
       </c>
       <c r="E38" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F38" t="s">
-        <v>372</v>
+        <v>215</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>373</v>
@@ -3857,7 +4898,7 @@
         <v>381</v>
       </c>
       <c r="C40" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="D40" t="s">
         <v>202</v>
@@ -3880,33 +4921,33 @@
         <v>386</v>
       </c>
       <c r="C41" t="s">
+        <v>218</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
         <v>387</v>
       </c>
-      <c r="D41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E41" t="s">
-        <v>360</v>
-      </c>
       <c r="F41" t="s">
+        <v>344</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>389</v>
+      </c>
+      <c r="B42" t="s">
         <v>390</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>391</v>
       </c>
-      <c r="C42" t="s">
-        <v>219</v>
-      </c>
       <c r="D42" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="E42" t="s">
         <v>392</v>
@@ -3923,22 +4964,22 @@
         <v>395</v>
       </c>
       <c r="B43" t="s">
-        <v>224</v>
+        <v>396</v>
       </c>
       <c r="C43" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D43" t="s">
         <v>202</v>
       </c>
       <c r="E43" t="s">
-        <v>272</v>
+        <v>397</v>
       </c>
       <c r="F43" t="s">
-        <v>227</v>
+        <v>398</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3946,321 +4987,321 @@
         <v>395</v>
       </c>
       <c r="B44" t="s">
-        <v>224</v>
+        <v>400</v>
       </c>
       <c r="C44" t="s">
-        <v>229</v>
+        <v>401</v>
       </c>
       <c r="D44" t="s">
         <v>202</v>
       </c>
       <c r="E44" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F44" t="s">
-        <v>227</v>
+        <v>402</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B45" t="s">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="D45" t="s">
         <v>202</v>
       </c>
       <c r="E45" t="s">
-        <v>220</v>
+        <v>406</v>
       </c>
       <c r="F45" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s">
-        <v>241</v>
+        <v>410</v>
       </c>
       <c r="C46" t="s">
-        <v>213</v>
+        <v>411</v>
       </c>
       <c r="D46" t="s">
         <v>202</v>
       </c>
       <c r="E46" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="F46" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C47" t="s">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="D47" t="s">
         <v>202</v>
       </c>
       <c r="E47" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F47" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C48" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D48" t="s">
         <v>202</v>
       </c>
       <c r="E48" t="s">
-        <v>226</v>
+        <v>421</v>
       </c>
       <c r="F48" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="B49" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="C49" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="D49" t="s">
         <v>202</v>
       </c>
       <c r="E49" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="F49" t="s">
-        <v>299</v>
+        <v>428</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B50" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="C50" t="s">
-        <v>207</v>
+        <v>432</v>
       </c>
       <c r="D50" t="s">
         <v>202</v>
       </c>
       <c r="E50" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="F50" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C51" t="s">
-        <v>256</v>
+        <v>438</v>
       </c>
       <c r="D51" t="s">
-        <v>426</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="F51" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C52" t="s">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="D52" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="E52" t="s">
-        <v>432</v>
+        <v>258</v>
       </c>
       <c r="F52" t="s">
-        <v>209</v>
+        <v>444</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="B53" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="C53" t="s">
-        <v>236</v>
+        <v>411</v>
       </c>
       <c r="D53" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="E53" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="F53" t="s">
-        <v>436</v>
+        <v>203</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C54" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="D54" t="s">
         <v>202</v>
       </c>
       <c r="E54" t="s">
-        <v>209</v>
+        <v>452</v>
       </c>
       <c r="F54" t="s">
-        <v>441</v>
+        <v>203</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s">
-        <v>241</v>
+        <v>455</v>
       </c>
       <c r="C55" t="s">
-        <v>213</v>
+        <v>456</v>
       </c>
       <c r="D55" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="E55" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="F55" t="s">
-        <v>209</v>
+        <v>458</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="C56" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="D56" t="s">
         <v>202</v>
       </c>
       <c r="E56" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>463</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="C57" t="s">
-        <v>448</v>
+        <v>290</v>
       </c>
       <c r="D57" t="s">
         <v>202</v>
       </c>
       <c r="E57" t="s">
-        <v>209</v>
+        <v>466</v>
       </c>
       <c r="F57" t="s">
-        <v>452</v>
+        <v>203</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4268,390 +5309,2483 @@
         <v>454</v>
       </c>
       <c r="B58" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="C58" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="D58" t="s">
         <v>202</v>
       </c>
       <c r="E58" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F58" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s">
-        <v>224</v>
+        <v>474</v>
       </c>
       <c r="C59" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D59" t="s">
         <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="F59" t="s">
-        <v>227</v>
+        <v>476</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s">
-        <v>224</v>
+        <v>479</v>
       </c>
       <c r="C60" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D60" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="E60" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="F60" t="s">
-        <v>227</v>
+        <v>481</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="B61" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="C61" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="D61" t="s">
         <v>202</v>
       </c>
       <c r="E61" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F61" t="s">
-        <v>399</v>
+        <v>203</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="B62" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="C62" t="s">
-        <v>219</v>
+        <v>485</v>
       </c>
       <c r="D62" t="s">
         <v>202</v>
       </c>
       <c r="E62" t="s">
-        <v>469</v>
+        <v>203</v>
       </c>
       <c r="F62" t="s">
-        <v>470</v>
+        <v>203</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="C63" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="D63" t="s">
         <v>202</v>
       </c>
       <c r="E63" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F63" t="s">
-        <v>452</v>
+        <v>203</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C64" t="s">
-        <v>207</v>
+        <v>493</v>
       </c>
       <c r="D64" t="s">
         <v>202</v>
       </c>
       <c r="E64" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="F64" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B65" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C65" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D65" t="s">
         <v>202</v>
       </c>
       <c r="E65" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="F65" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="B66" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="C66" t="s">
-        <v>486</v>
+        <v>218</v>
       </c>
       <c r="D66" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="E66" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="F66" t="s">
-        <v>209</v>
+        <v>502</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s">
-        <v>431</v>
+        <v>505</v>
       </c>
       <c r="C67" t="s">
-        <v>236</v>
+        <v>506</v>
       </c>
       <c r="D67" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="E67" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="F67" t="s">
-        <v>209</v>
+        <v>508</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="C68" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D68" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="E68" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="F68" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="B69" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="C69" t="s">
-        <v>500</v>
+        <v>218</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>313</v>
       </c>
       <c r="E69" t="s">
-        <v>209</v>
+        <v>518</v>
       </c>
       <c r="F69" t="s">
-        <v>299</v>
+        <v>519</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="B70" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="C70" t="s">
-        <v>207</v>
+        <v>523</v>
       </c>
       <c r="D70" t="s">
         <v>202</v>
       </c>
       <c r="E70" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="F70" t="s">
-        <v>204</v>
+        <v>525</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B71" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="C71" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D71" t="s">
         <v>202</v>
       </c>
       <c r="E71" t="s">
-        <v>209</v>
+        <v>529</v>
       </c>
       <c r="F71" t="s">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="B72" t="s">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="C72" t="s">
-        <v>213</v>
+        <v>534</v>
       </c>
       <c r="D72" t="s">
-        <v>262</v>
+        <v>349</v>
       </c>
       <c r="E72" t="s">
-        <v>512</v>
+        <v>203</v>
       </c>
       <c r="F72" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="B73" t="s">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="C73" t="s">
-        <v>207</v>
+        <v>539</v>
       </c>
       <c r="D73" t="s">
         <v>202</v>
       </c>
       <c r="E73" t="s">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="F73" t="s">
-        <v>518</v>
+        <v>541</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>519</v>
+        <v>542</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="B74" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="C74" t="s">
-        <v>213</v>
+        <v>543</v>
       </c>
       <c r="D74" t="s">
         <v>202</v>
       </c>
       <c r="E74" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="F74" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>524</v>
+        <v>544</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>537</v>
+      </c>
+      <c r="B75" t="s">
+        <v>538</v>
+      </c>
+      <c r="C75" t="s">
+        <v>545</v>
+      </c>
+      <c r="D75" t="s">
+        <v>202</v>
+      </c>
+      <c r="E75" t="s">
+        <v>540</v>
+      </c>
+      <c r="F75" t="s">
+        <v>541</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>537</v>
+      </c>
+      <c r="B76" t="s">
+        <v>538</v>
+      </c>
+      <c r="C76" t="s">
+        <v>547</v>
+      </c>
+      <c r="D76" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" t="s">
+        <v>540</v>
+      </c>
+      <c r="F76" t="s">
+        <v>541</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>537</v>
+      </c>
+      <c r="B77" t="s">
+        <v>538</v>
+      </c>
+      <c r="C77" t="s">
+        <v>549</v>
+      </c>
+      <c r="D77" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" t="s">
+        <v>540</v>
+      </c>
+      <c r="F77" t="s">
+        <v>541</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>537</v>
+      </c>
+      <c r="B78" t="s">
+        <v>538</v>
+      </c>
+      <c r="C78" t="s">
+        <v>551</v>
+      </c>
+      <c r="D78" t="s">
+        <v>202</v>
+      </c>
+      <c r="E78" t="s">
+        <v>540</v>
+      </c>
+      <c r="F78" t="s">
+        <v>541</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>537</v>
+      </c>
+      <c r="B79" t="s">
+        <v>538</v>
+      </c>
+      <c r="C79" t="s">
+        <v>553</v>
+      </c>
+      <c r="D79" t="s">
+        <v>202</v>
+      </c>
+      <c r="E79" t="s">
+        <v>540</v>
+      </c>
+      <c r="F79" t="s">
+        <v>541</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>537</v>
+      </c>
+      <c r="B80" t="s">
+        <v>538</v>
+      </c>
+      <c r="C80" t="s">
+        <v>555</v>
+      </c>
+      <c r="D80" t="s">
+        <v>202</v>
+      </c>
+      <c r="E80" t="s">
+        <v>540</v>
+      </c>
+      <c r="F80" t="s">
+        <v>541</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>537</v>
+      </c>
+      <c r="B81" t="s">
+        <v>538</v>
+      </c>
+      <c r="C81" t="s">
+        <v>557</v>
+      </c>
+      <c r="D81" t="s">
+        <v>202</v>
+      </c>
+      <c r="E81" t="s">
+        <v>540</v>
+      </c>
+      <c r="F81" t="s">
+        <v>541</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>537</v>
+      </c>
+      <c r="B82" t="s">
+        <v>538</v>
+      </c>
+      <c r="C82" t="s">
+        <v>223</v>
+      </c>
+      <c r="D82" t="s">
+        <v>202</v>
+      </c>
+      <c r="E82" t="s">
+        <v>540</v>
+      </c>
+      <c r="F82" t="s">
+        <v>541</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>537</v>
+      </c>
+      <c r="B83" t="s">
+        <v>538</v>
+      </c>
+      <c r="C83" t="s">
+        <v>560</v>
+      </c>
+      <c r="D83" t="s">
+        <v>202</v>
+      </c>
+      <c r="E83" t="s">
+        <v>540</v>
+      </c>
+      <c r="F83" t="s">
+        <v>541</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>537</v>
+      </c>
+      <c r="B84" t="s">
+        <v>538</v>
+      </c>
+      <c r="C84" t="s">
+        <v>562</v>
+      </c>
+      <c r="D84" t="s">
+        <v>202</v>
+      </c>
+      <c r="E84" t="s">
+        <v>540</v>
+      </c>
+      <c r="F84" t="s">
+        <v>541</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>537</v>
+      </c>
+      <c r="B85" t="s">
+        <v>538</v>
+      </c>
+      <c r="C85" t="s">
+        <v>564</v>
+      </c>
+      <c r="D85" t="s">
+        <v>202</v>
+      </c>
+      <c r="E85" t="s">
+        <v>540</v>
+      </c>
+      <c r="F85" t="s">
+        <v>541</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>537</v>
+      </c>
+      <c r="B86" t="s">
+        <v>538</v>
+      </c>
+      <c r="C86" t="s">
+        <v>566</v>
+      </c>
+      <c r="D86" t="s">
+        <v>202</v>
+      </c>
+      <c r="E86" t="s">
+        <v>540</v>
+      </c>
+      <c r="F86" t="s">
+        <v>541</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>537</v>
+      </c>
+      <c r="B87" t="s">
+        <v>538</v>
+      </c>
+      <c r="C87" t="s">
+        <v>568</v>
+      </c>
+      <c r="D87" t="s">
+        <v>202</v>
+      </c>
+      <c r="E87" t="s">
+        <v>540</v>
+      </c>
+      <c r="F87" t="s">
+        <v>541</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>537</v>
+      </c>
+      <c r="B88" t="s">
+        <v>538</v>
+      </c>
+      <c r="C88" t="s">
+        <v>570</v>
+      </c>
+      <c r="D88" t="s">
+        <v>202</v>
+      </c>
+      <c r="E88" t="s">
+        <v>540</v>
+      </c>
+      <c r="F88" t="s">
+        <v>541</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>537</v>
+      </c>
+      <c r="B89" t="s">
+        <v>538</v>
+      </c>
+      <c r="C89" t="s">
+        <v>572</v>
+      </c>
+      <c r="D89" t="s">
+        <v>202</v>
+      </c>
+      <c r="E89" t="s">
+        <v>540</v>
+      </c>
+      <c r="F89" t="s">
+        <v>541</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>537</v>
+      </c>
+      <c r="B90" t="s">
+        <v>538</v>
+      </c>
+      <c r="C90" t="s">
+        <v>574</v>
+      </c>
+      <c r="D90" t="s">
+        <v>202</v>
+      </c>
+      <c r="E90" t="s">
+        <v>540</v>
+      </c>
+      <c r="F90" t="s">
+        <v>541</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>537</v>
+      </c>
+      <c r="B91" t="s">
+        <v>538</v>
+      </c>
+      <c r="C91" t="s">
+        <v>576</v>
+      </c>
+      <c r="D91" t="s">
+        <v>202</v>
+      </c>
+      <c r="E91" t="s">
+        <v>540</v>
+      </c>
+      <c r="F91" t="s">
+        <v>541</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>578</v>
+      </c>
+      <c r="B92" t="s">
+        <v>579</v>
+      </c>
+      <c r="C92" t="s">
+        <v>580</v>
+      </c>
+      <c r="D92" t="s">
+        <v>202</v>
+      </c>
+      <c r="E92" t="s">
+        <v>498</v>
+      </c>
+      <c r="F92" t="s">
+        <v>581</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>583</v>
+      </c>
+      <c r="B93" t="s">
+        <v>584</v>
+      </c>
+      <c r="C93" t="s">
+        <v>229</v>
+      </c>
+      <c r="D93" t="s">
+        <v>202</v>
+      </c>
+      <c r="E93" t="s">
+        <v>585</v>
+      </c>
+      <c r="F93" t="s">
+        <v>586</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>588</v>
+      </c>
+      <c r="B94" t="s">
+        <v>234</v>
+      </c>
+      <c r="C94" t="s">
+        <v>235</v>
+      </c>
+      <c r="D94" t="s">
+        <v>202</v>
+      </c>
+      <c r="E94" t="s">
+        <v>329</v>
+      </c>
+      <c r="F94" t="s">
+        <v>237</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>588</v>
+      </c>
+      <c r="B95" t="s">
+        <v>234</v>
+      </c>
+      <c r="C95" t="s">
+        <v>239</v>
+      </c>
+      <c r="D95" t="s">
+        <v>202</v>
+      </c>
+      <c r="E95" t="s">
+        <v>329</v>
+      </c>
+      <c r="F95" t="s">
+        <v>237</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>591</v>
+      </c>
+      <c r="B96" t="s">
+        <v>228</v>
+      </c>
+      <c r="C96" t="s">
+        <v>229</v>
+      </c>
+      <c r="D96" t="s">
+        <v>202</v>
+      </c>
+      <c r="E96" t="s">
+        <v>230</v>
+      </c>
+      <c r="F96" t="s">
+        <v>592</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>594</v>
+      </c>
+      <c r="B97" t="s">
+        <v>251</v>
+      </c>
+      <c r="C97" t="s">
+        <v>223</v>
+      </c>
+      <c r="D97" t="s">
+        <v>202</v>
+      </c>
+      <c r="E97" t="s">
+        <v>595</v>
+      </c>
+      <c r="F97" t="s">
+        <v>203</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>594</v>
+      </c>
+      <c r="B98" t="s">
+        <v>254</v>
+      </c>
+      <c r="C98" t="s">
+        <v>223</v>
+      </c>
+      <c r="D98" t="s">
+        <v>202</v>
+      </c>
+      <c r="E98" t="s">
+        <v>595</v>
+      </c>
+      <c r="F98" t="s">
+        <v>203</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>598</v>
+      </c>
+      <c r="B99" t="s">
+        <v>599</v>
+      </c>
+      <c r="C99" t="s">
+        <v>246</v>
+      </c>
+      <c r="D99" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99" t="s">
+        <v>600</v>
+      </c>
+      <c r="F99" t="s">
+        <v>601</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>603</v>
+      </c>
+      <c r="B100" t="s">
+        <v>604</v>
+      </c>
+      <c r="C100" t="s">
+        <v>290</v>
+      </c>
+      <c r="D100" t="s">
+        <v>202</v>
+      </c>
+      <c r="E100" t="s">
+        <v>203</v>
+      </c>
+      <c r="F100" t="s">
+        <v>344</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>606</v>
+      </c>
+      <c r="B101" t="s">
+        <v>607</v>
+      </c>
+      <c r="C101" t="s">
+        <v>608</v>
+      </c>
+      <c r="D101" t="s">
+        <v>202</v>
+      </c>
+      <c r="E101" t="s">
+        <v>236</v>
+      </c>
+      <c r="F101" t="s">
+        <v>609</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>611</v>
+      </c>
+      <c r="B102" t="s">
+        <v>612</v>
+      </c>
+      <c r="C102" t="s">
+        <v>613</v>
+      </c>
+      <c r="D102" t="s">
+        <v>202</v>
+      </c>
+      <c r="E102" t="s">
+        <v>614</v>
+      </c>
+      <c r="F102" t="s">
+        <v>615</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>617</v>
+      </c>
+      <c r="B103" t="s">
+        <v>618</v>
+      </c>
+      <c r="C103" t="s">
+        <v>619</v>
+      </c>
+      <c r="D103" t="s">
+        <v>202</v>
+      </c>
+      <c r="E103" t="s">
+        <v>620</v>
+      </c>
+      <c r="F103" t="s">
+        <v>367</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>622</v>
+      </c>
+      <c r="B104" t="s">
+        <v>623</v>
+      </c>
+      <c r="C104" t="s">
+        <v>235</v>
+      </c>
+      <c r="D104" t="s">
+        <v>313</v>
+      </c>
+      <c r="E104" t="s">
+        <v>624</v>
+      </c>
+      <c r="F104" t="s">
+        <v>625</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>627</v>
+      </c>
+      <c r="B105" t="s">
+        <v>628</v>
+      </c>
+      <c r="C105" t="s">
+        <v>339</v>
+      </c>
+      <c r="D105" t="s">
+        <v>202</v>
+      </c>
+      <c r="E105" t="s">
+        <v>629</v>
+      </c>
+      <c r="F105" t="s">
+        <v>630</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>632</v>
+      </c>
+      <c r="B106" t="s">
+        <v>633</v>
+      </c>
+      <c r="C106" t="s">
+        <v>223</v>
+      </c>
+      <c r="D106" t="s">
+        <v>202</v>
+      </c>
+      <c r="E106" t="s">
+        <v>634</v>
+      </c>
+      <c r="F106" t="s">
+        <v>635</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>637</v>
+      </c>
+      <c r="B107" t="s">
+        <v>638</v>
+      </c>
+      <c r="C107" t="s">
+        <v>229</v>
+      </c>
+      <c r="D107" t="s">
+        <v>202</v>
+      </c>
+      <c r="E107" t="s">
+        <v>639</v>
+      </c>
+      <c r="F107" t="s">
+        <v>640</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>642</v>
+      </c>
+      <c r="B108" t="s">
+        <v>643</v>
+      </c>
+      <c r="C108" t="s">
+        <v>644</v>
+      </c>
+      <c r="D108" t="s">
+        <v>645</v>
+      </c>
+      <c r="E108" t="s">
+        <v>350</v>
+      </c>
+      <c r="F108" t="s">
+        <v>646</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>648</v>
+      </c>
+      <c r="B109" t="s">
+        <v>649</v>
+      </c>
+      <c r="C109" t="s">
+        <v>650</v>
+      </c>
+      <c r="D109" t="s">
+        <v>202</v>
+      </c>
+      <c r="E109" t="s">
+        <v>651</v>
+      </c>
+      <c r="F109" t="s">
+        <v>508</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>653</v>
+      </c>
+      <c r="B110" t="s">
+        <v>654</v>
+      </c>
+      <c r="C110" t="s">
+        <v>218</v>
+      </c>
+      <c r="D110" t="s">
+        <v>202</v>
+      </c>
+      <c r="E110" t="s">
+        <v>655</v>
+      </c>
+      <c r="F110" t="s">
+        <v>656</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111" t="s">
+        <v>658</v>
+      </c>
+      <c r="C111" t="s">
+        <v>268</v>
+      </c>
+      <c r="D111" t="s">
+        <v>202</v>
+      </c>
+      <c r="E111" t="s">
+        <v>498</v>
+      </c>
+      <c r="F111" t="s">
+        <v>659</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>128</v>
+      </c>
+      <c r="B112" t="s">
+        <v>661</v>
+      </c>
+      <c r="C112" t="s">
+        <v>551</v>
+      </c>
+      <c r="D112" t="s">
+        <v>202</v>
+      </c>
+      <c r="E112" t="s">
+        <v>662</v>
+      </c>
+      <c r="F112" t="s">
+        <v>663</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>665</v>
+      </c>
+      <c r="B113" t="s">
+        <v>666</v>
+      </c>
+      <c r="C113" t="s">
+        <v>235</v>
+      </c>
+      <c r="D113" t="s">
+        <v>202</v>
+      </c>
+      <c r="E113" t="s">
+        <v>667</v>
+      </c>
+      <c r="F113" t="s">
+        <v>668</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>670</v>
+      </c>
+      <c r="B114" t="s">
+        <v>273</v>
+      </c>
+      <c r="C114" t="s">
+        <v>235</v>
+      </c>
+      <c r="D114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E114" t="s">
+        <v>671</v>
+      </c>
+      <c r="F114" t="s">
+        <v>672</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>674</v>
+      </c>
+      <c r="B115" t="s">
+        <v>675</v>
+      </c>
+      <c r="C115" t="s">
+        <v>290</v>
+      </c>
+      <c r="D115" t="s">
+        <v>645</v>
+      </c>
+      <c r="E115" t="s">
+        <v>676</v>
+      </c>
+      <c r="F115" t="s">
+        <v>677</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>679</v>
+      </c>
+      <c r="B116" t="s">
+        <v>680</v>
+      </c>
+      <c r="C116" t="s">
+        <v>246</v>
+      </c>
+      <c r="D116" t="s">
+        <v>307</v>
+      </c>
+      <c r="E116" t="s">
+        <v>681</v>
+      </c>
+      <c r="F116" t="s">
+        <v>203</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>683</v>
+      </c>
+      <c r="B117" t="s">
+        <v>680</v>
+      </c>
+      <c r="C117" t="s">
+        <v>246</v>
+      </c>
+      <c r="D117" t="s">
+        <v>307</v>
+      </c>
+      <c r="E117" t="s">
+        <v>684</v>
+      </c>
+      <c r="F117" t="s">
+        <v>270</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>686</v>
+      </c>
+      <c r="B118" t="s">
+        <v>687</v>
+      </c>
+      <c r="C118" t="s">
+        <v>268</v>
+      </c>
+      <c r="D118" t="s">
+        <v>307</v>
+      </c>
+      <c r="E118" t="s">
+        <v>688</v>
+      </c>
+      <c r="F118" t="s">
+        <v>689</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>691</v>
+      </c>
+      <c r="B119" t="s">
+        <v>692</v>
+      </c>
+      <c r="C119" t="s">
+        <v>279</v>
+      </c>
+      <c r="D119" t="s">
+        <v>202</v>
+      </c>
+      <c r="E119" t="s">
+        <v>693</v>
+      </c>
+      <c r="F119" t="s">
+        <v>694</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>696</v>
+      </c>
+      <c r="B120" t="s">
+        <v>623</v>
+      </c>
+      <c r="C120" t="s">
+        <v>235</v>
+      </c>
+      <c r="D120" t="s">
+        <v>202</v>
+      </c>
+      <c r="E120" t="s">
+        <v>697</v>
+      </c>
+      <c r="F120" t="s">
+        <v>625</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>699</v>
+      </c>
+      <c r="B121" t="s">
+        <v>700</v>
+      </c>
+      <c r="C121" t="s">
+        <v>701</v>
+      </c>
+      <c r="D121" t="s">
+        <v>202</v>
+      </c>
+      <c r="E121" t="s">
+        <v>702</v>
+      </c>
+      <c r="F121" t="s">
+        <v>703</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>705</v>
+      </c>
+      <c r="B122" t="s">
+        <v>706</v>
+      </c>
+      <c r="C122" t="s">
+        <v>218</v>
+      </c>
+      <c r="D122" t="s">
+        <v>645</v>
+      </c>
+      <c r="E122" t="s">
+        <v>707</v>
+      </c>
+      <c r="F122" t="s">
+        <v>708</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>710</v>
+      </c>
+      <c r="B123" t="s">
+        <v>711</v>
+      </c>
+      <c r="C123" t="s">
+        <v>229</v>
+      </c>
+      <c r="D123" t="s">
+        <v>202</v>
+      </c>
+      <c r="E123" t="s">
+        <v>712</v>
+      </c>
+      <c r="F123" t="s">
+        <v>713</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>715</v>
+      </c>
+      <c r="B124" t="s">
+        <v>716</v>
+      </c>
+      <c r="C124" t="s">
+        <v>235</v>
+      </c>
+      <c r="D124" t="s">
+        <v>202</v>
+      </c>
+      <c r="E124" t="s">
+        <v>717</v>
+      </c>
+      <c r="F124" t="s">
+        <v>718</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>720</v>
+      </c>
+      <c r="B125" t="s">
+        <v>721</v>
+      </c>
+      <c r="C125" t="s">
+        <v>722</v>
+      </c>
+      <c r="D125" t="s">
+        <v>202</v>
+      </c>
+      <c r="E125" t="s">
+        <v>203</v>
+      </c>
+      <c r="F125" t="s">
+        <v>723</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>725</v>
+      </c>
+      <c r="B126" t="s">
+        <v>251</v>
+      </c>
+      <c r="C126" t="s">
+        <v>223</v>
+      </c>
+      <c r="D126" t="s">
+        <v>202</v>
+      </c>
+      <c r="E126" t="s">
+        <v>726</v>
+      </c>
+      <c r="F126" t="s">
+        <v>203</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>725</v>
+      </c>
+      <c r="B127" t="s">
+        <v>254</v>
+      </c>
+      <c r="C127" t="s">
+        <v>223</v>
+      </c>
+      <c r="D127" t="s">
+        <v>202</v>
+      </c>
+      <c r="E127" t="s">
+        <v>726</v>
+      </c>
+      <c r="F127" t="s">
+        <v>203</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>729</v>
+      </c>
+      <c r="B128" t="s">
+        <v>730</v>
+      </c>
+      <c r="C128" t="s">
+        <v>229</v>
+      </c>
+      <c r="D128" t="s">
+        <v>202</v>
+      </c>
+      <c r="E128" t="s">
+        <v>203</v>
+      </c>
+      <c r="F128" t="s">
+        <v>203</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>732</v>
+      </c>
+      <c r="B129" t="s">
+        <v>733</v>
+      </c>
+      <c r="C129" t="s">
+        <v>734</v>
+      </c>
+      <c r="D129" t="s">
+        <v>307</v>
+      </c>
+      <c r="E129" t="s">
+        <v>203</v>
+      </c>
+      <c r="F129" t="s">
+        <v>735</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>737</v>
+      </c>
+      <c r="B130" t="s">
+        <v>738</v>
+      </c>
+      <c r="C130" t="s">
+        <v>739</v>
+      </c>
+      <c r="D130" t="s">
+        <v>202</v>
+      </c>
+      <c r="E130" t="s">
+        <v>740</v>
+      </c>
+      <c r="F130" t="s">
+        <v>203</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>742</v>
+      </c>
+      <c r="B131" t="s">
+        <v>738</v>
+      </c>
+      <c r="C131" t="s">
+        <v>739</v>
+      </c>
+      <c r="D131" t="s">
+        <v>202</v>
+      </c>
+      <c r="E131" t="s">
+        <v>203</v>
+      </c>
+      <c r="F131" t="s">
+        <v>743</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>745</v>
+      </c>
+      <c r="B132" t="s">
+        <v>628</v>
+      </c>
+      <c r="C132" t="s">
+        <v>339</v>
+      </c>
+      <c r="D132" t="s">
+        <v>202</v>
+      </c>
+      <c r="E132" t="s">
+        <v>629</v>
+      </c>
+      <c r="F132" t="s">
+        <v>630</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>747</v>
+      </c>
+      <c r="B133" t="s">
+        <v>748</v>
+      </c>
+      <c r="C133" t="s">
+        <v>749</v>
+      </c>
+      <c r="D133" t="s">
+        <v>202</v>
+      </c>
+      <c r="E133" t="s">
+        <v>750</v>
+      </c>
+      <c r="F133" t="s">
+        <v>751</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>753</v>
+      </c>
+      <c r="B134" t="s">
+        <v>754</v>
+      </c>
+      <c r="C134" t="s">
+        <v>739</v>
+      </c>
+      <c r="D134" t="s">
+        <v>202</v>
+      </c>
+      <c r="E134" t="s">
+        <v>755</v>
+      </c>
+      <c r="F134" t="s">
+        <v>756</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>758</v>
+      </c>
+      <c r="B135" t="s">
+        <v>759</v>
+      </c>
+      <c r="C135" t="s">
+        <v>555</v>
+      </c>
+      <c r="D135" t="s">
+        <v>202</v>
+      </c>
+      <c r="E135" t="s">
+        <v>203</v>
+      </c>
+      <c r="F135" t="s">
+        <v>760</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>762</v>
+      </c>
+      <c r="B136" t="s">
+        <v>234</v>
+      </c>
+      <c r="C136" t="s">
+        <v>235</v>
+      </c>
+      <c r="D136" t="s">
+        <v>202</v>
+      </c>
+      <c r="E136" t="s">
+        <v>763</v>
+      </c>
+      <c r="F136" t="s">
+        <v>237</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>762</v>
+      </c>
+      <c r="B137" t="s">
+        <v>234</v>
+      </c>
+      <c r="C137" t="s">
+        <v>239</v>
+      </c>
+      <c r="D137" t="s">
+        <v>202</v>
+      </c>
+      <c r="E137" t="s">
+        <v>763</v>
+      </c>
+      <c r="F137" t="s">
+        <v>237</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>766</v>
+      </c>
+      <c r="B138" t="s">
+        <v>767</v>
+      </c>
+      <c r="C138" t="s">
+        <v>739</v>
+      </c>
+      <c r="D138" t="s">
+        <v>202</v>
+      </c>
+      <c r="E138" t="s">
+        <v>203</v>
+      </c>
+      <c r="F138" t="s">
+        <v>592</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>769</v>
+      </c>
+      <c r="B139" t="s">
+        <v>770</v>
+      </c>
+      <c r="C139" t="s">
+        <v>229</v>
+      </c>
+      <c r="D139" t="s">
+        <v>202</v>
+      </c>
+      <c r="E139" t="s">
+        <v>771</v>
+      </c>
+      <c r="F139" t="s">
+        <v>772</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>774</v>
+      </c>
+      <c r="B140" t="s">
+        <v>738</v>
+      </c>
+      <c r="C140" t="s">
+        <v>739</v>
+      </c>
+      <c r="D140" t="s">
+        <v>202</v>
+      </c>
+      <c r="E140" t="s">
+        <v>203</v>
+      </c>
+      <c r="F140" t="s">
+        <v>743</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>776</v>
+      </c>
+      <c r="B141" t="s">
+        <v>777</v>
+      </c>
+      <c r="C141" t="s">
+        <v>218</v>
+      </c>
+      <c r="D141" t="s">
+        <v>202</v>
+      </c>
+      <c r="E141" t="s">
+        <v>778</v>
+      </c>
+      <c r="F141" t="s">
+        <v>779</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>781</v>
+      </c>
+      <c r="B142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C142" t="s">
+        <v>411</v>
+      </c>
+      <c r="D142" t="s">
+        <v>202</v>
+      </c>
+      <c r="E142" t="s">
+        <v>782</v>
+      </c>
+      <c r="F142" t="s">
+        <v>203</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>784</v>
+      </c>
+      <c r="B143" t="s">
+        <v>785</v>
+      </c>
+      <c r="C143" t="s">
+        <v>223</v>
+      </c>
+      <c r="D143" t="s">
+        <v>202</v>
+      </c>
+      <c r="E143" t="s">
+        <v>786</v>
+      </c>
+      <c r="F143" t="s">
+        <v>787</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>789</v>
+      </c>
+      <c r="B144" t="s">
+        <v>790</v>
+      </c>
+      <c r="C144" t="s">
+        <v>229</v>
+      </c>
+      <c r="D144" t="s">
+        <v>202</v>
+      </c>
+      <c r="E144" t="s">
+        <v>791</v>
+      </c>
+      <c r="F144" t="s">
+        <v>792</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>794</v>
+      </c>
+      <c r="B145" t="s">
+        <v>795</v>
+      </c>
+      <c r="C145" t="s">
+        <v>229</v>
+      </c>
+      <c r="D145" t="s">
+        <v>202</v>
+      </c>
+      <c r="E145" t="s">
+        <v>796</v>
+      </c>
+      <c r="F145" t="s">
+        <v>797</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>799</v>
+      </c>
+      <c r="B146" t="s">
+        <v>800</v>
+      </c>
+      <c r="C146" t="s">
+        <v>801</v>
+      </c>
+      <c r="D146" t="s">
+        <v>307</v>
+      </c>
+      <c r="E146" t="s">
+        <v>802</v>
+      </c>
+      <c r="F146" t="s">
+        <v>203</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>804</v>
+      </c>
+      <c r="B147" t="s">
+        <v>680</v>
+      </c>
+      <c r="C147" t="s">
+        <v>246</v>
+      </c>
+      <c r="D147" t="s">
+        <v>307</v>
+      </c>
+      <c r="E147" t="s">
+        <v>805</v>
+      </c>
+      <c r="F147" t="s">
+        <v>203</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>807</v>
+      </c>
+      <c r="B148" t="s">
+        <v>808</v>
+      </c>
+      <c r="C148" t="s">
+        <v>574</v>
+      </c>
+      <c r="D148" t="s">
+        <v>202</v>
+      </c>
+      <c r="E148" t="s">
+        <v>809</v>
+      </c>
+      <c r="F148" t="s">
+        <v>810</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>812</v>
+      </c>
+      <c r="B149" t="s">
+        <v>273</v>
+      </c>
+      <c r="C149" t="s">
+        <v>235</v>
+      </c>
+      <c r="D149" t="s">
+        <v>202</v>
+      </c>
+      <c r="E149" t="s">
+        <v>274</v>
+      </c>
+      <c r="F149" t="s">
+        <v>203</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>814</v>
+      </c>
+      <c r="B150" t="s">
+        <v>815</v>
+      </c>
+      <c r="C150" t="s">
+        <v>268</v>
+      </c>
+      <c r="D150" t="s">
+        <v>202</v>
+      </c>
+      <c r="E150" t="s">
+        <v>816</v>
+      </c>
+      <c r="F150" t="s">
+        <v>817</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>819</v>
+      </c>
+      <c r="B151" t="s">
+        <v>820</v>
+      </c>
+      <c r="C151" t="s">
+        <v>229</v>
+      </c>
+      <c r="D151" t="s">
+        <v>349</v>
+      </c>
+      <c r="E151" t="s">
+        <v>203</v>
+      </c>
+      <c r="F151" t="s">
+        <v>821</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>823</v>
+      </c>
+      <c r="B152" t="s">
+        <v>824</v>
+      </c>
+      <c r="C152" t="s">
+        <v>825</v>
+      </c>
+      <c r="D152" t="s">
+        <v>202</v>
+      </c>
+      <c r="E152" t="s">
+        <v>203</v>
+      </c>
+      <c r="F152" t="s">
+        <v>367</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>827</v>
+      </c>
+      <c r="B153" t="s">
+        <v>628</v>
+      </c>
+      <c r="C153" t="s">
+        <v>339</v>
+      </c>
+      <c r="D153" t="s">
+        <v>202</v>
+      </c>
+      <c r="E153" t="s">
+        <v>629</v>
+      </c>
+      <c r="F153" t="s">
+        <v>630</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>829</v>
+      </c>
+      <c r="B154" t="s">
+        <v>830</v>
+      </c>
+      <c r="C154" t="s">
+        <v>218</v>
+      </c>
+      <c r="D154" t="s">
+        <v>202</v>
+      </c>
+      <c r="E154" t="s">
+        <v>831</v>
+      </c>
+      <c r="F154" t="s">
+        <v>215</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>833</v>
+      </c>
+      <c r="B155" t="s">
+        <v>484</v>
+      </c>
+      <c r="C155" t="s">
+        <v>485</v>
+      </c>
+      <c r="D155" t="s">
+        <v>202</v>
+      </c>
+      <c r="E155" t="s">
+        <v>203</v>
+      </c>
+      <c r="F155" t="s">
+        <v>203</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>835</v>
+      </c>
+      <c r="B156" t="s">
+        <v>484</v>
+      </c>
+      <c r="C156" t="s">
+        <v>485</v>
+      </c>
+      <c r="D156" t="s">
+        <v>202</v>
+      </c>
+      <c r="E156" t="s">
+        <v>203</v>
+      </c>
+      <c r="F156" t="s">
+        <v>203</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>837</v>
+      </c>
+      <c r="B157" t="s">
+        <v>484</v>
+      </c>
+      <c r="C157" t="s">
+        <v>485</v>
+      </c>
+      <c r="D157" t="s">
+        <v>202</v>
+      </c>
+      <c r="E157" t="s">
+        <v>203</v>
+      </c>
+      <c r="F157" t="s">
+        <v>203</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>839</v>
+      </c>
+      <c r="B158" t="s">
+        <v>484</v>
+      </c>
+      <c r="C158" t="s">
+        <v>485</v>
+      </c>
+      <c r="D158" t="s">
+        <v>202</v>
+      </c>
+      <c r="E158" t="s">
+        <v>203</v>
+      </c>
+      <c r="F158" t="s">
+        <v>203</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>841</v>
+      </c>
+      <c r="B159" t="s">
+        <v>666</v>
+      </c>
+      <c r="C159" t="s">
+        <v>235</v>
+      </c>
+      <c r="D159" t="s">
+        <v>313</v>
+      </c>
+      <c r="E159" t="s">
+        <v>842</v>
+      </c>
+      <c r="F159" t="s">
+        <v>668</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>844</v>
+      </c>
+      <c r="B160" t="s">
+        <v>845</v>
+      </c>
+      <c r="C160" t="s">
+        <v>218</v>
+      </c>
+      <c r="D160" t="s">
+        <v>202</v>
+      </c>
+      <c r="E160" t="s">
+        <v>203</v>
+      </c>
+      <c r="F160" t="s">
+        <v>846</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>848</v>
+      </c>
+      <c r="B161" t="s">
+        <v>849</v>
+      </c>
+      <c r="C161" t="s">
+        <v>223</v>
+      </c>
+      <c r="D161" t="s">
+        <v>313</v>
+      </c>
+      <c r="E161" t="s">
+        <v>850</v>
+      </c>
+      <c r="F161" t="s">
+        <v>851</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>853</v>
+      </c>
+      <c r="B162" t="s">
+        <v>854</v>
+      </c>
+      <c r="C162" t="s">
+        <v>218</v>
+      </c>
+      <c r="D162" t="s">
+        <v>202</v>
+      </c>
+      <c r="E162" t="s">
+        <v>855</v>
+      </c>
+      <c r="F162" t="s">
+        <v>856</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>858</v>
+      </c>
+      <c r="B163" t="s">
+        <v>859</v>
+      </c>
+      <c r="C163" t="s">
+        <v>860</v>
+      </c>
+      <c r="D163" t="s">
+        <v>202</v>
+      </c>
+      <c r="E163" t="s">
+        <v>861</v>
+      </c>
+      <c r="F163" t="s">
+        <v>862</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>864</v>
+      </c>
+      <c r="B164" t="s">
+        <v>865</v>
+      </c>
+      <c r="C164" t="s">
+        <v>223</v>
+      </c>
+      <c r="D164" t="s">
+        <v>202</v>
+      </c>
+      <c r="E164" t="s">
+        <v>866</v>
+      </c>
+      <c r="F164" t="s">
+        <v>867</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>869</v>
+      </c>
+      <c r="B165" t="s">
+        <v>257</v>
+      </c>
+      <c r="C165" t="s">
+        <v>218</v>
+      </c>
+      <c r="D165" t="s">
+        <v>202</v>
+      </c>
+      <c r="E165" t="s">
+        <v>258</v>
+      </c>
+      <c r="F165" t="s">
+        <v>870</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -4730,6 +7864,97 @@
     <hyperlink ref="H72" r:id="rId71"/>
     <hyperlink ref="H73" r:id="rId72"/>
     <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
+    <hyperlink ref="H150" r:id="rId149"/>
+    <hyperlink ref="H151" r:id="rId150"/>
+    <hyperlink ref="H152" r:id="rId151"/>
+    <hyperlink ref="H153" r:id="rId152"/>
+    <hyperlink ref="H154" r:id="rId153"/>
+    <hyperlink ref="H155" r:id="rId154"/>
+    <hyperlink ref="H156" r:id="rId155"/>
+    <hyperlink ref="H157" r:id="rId156"/>
+    <hyperlink ref="H158" r:id="rId157"/>
+    <hyperlink ref="H159" r:id="rId158"/>
+    <hyperlink ref="H160" r:id="rId159"/>
+    <hyperlink ref="H161" r:id="rId160"/>
+    <hyperlink ref="H162" r:id="rId161"/>
+    <hyperlink ref="H163" r:id="rId162"/>
+    <hyperlink ref="H164" r:id="rId163"/>
+    <hyperlink ref="H165" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
